--- a/tests/indicators/indicator_manual_calcs.xlsx
+++ b/tests/indicators/indicator_manual_calcs.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\frkor\Desktop\Stockie\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:2001_{0D17526B-752F-4B79-97F5-42C0DC99EF84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AFC671D-951D-468F-9BFF-33DB72F67318}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4395" yWindow="3195" windowWidth="29790" windowHeight="14760" tabRatio="787" firstSheet="8" activeTab="21" xr2:uid="{0D315D7D-D057-4BD7-B5D6-896636B09A34}"/>
+    <workbookView xWindow="11115" yWindow="675" windowWidth="45480" windowHeight="19965" tabRatio="787" firstSheet="11" activeTab="28" xr2:uid="{0D315D7D-D057-4BD7-B5D6-896636B09A34}"/>
   </bookViews>
   <sheets>
     <sheet name="aapl" sheetId="2" r:id="rId1"/>
@@ -35,13 +35,18 @@
     <sheet name="pvt_tsla" sheetId="22" r:id="rId20"/>
     <sheet name="obv_tsla" sheetId="23" r:id="rId21"/>
     <sheet name="cmf_5_tsla" sheetId="24" r:id="rId22"/>
-    <sheet name="Sheet17" sheetId="25" r:id="rId23"/>
+    <sheet name="beta_5_tsla" sheetId="25" r:id="rId23"/>
+    <sheet name="rolling_volatility_5_aapl" sheetId="26" r:id="rId24"/>
+    <sheet name="downside_deviation_5_tsla" sheetId="27" r:id="rId25"/>
+    <sheet name="sharpe_5_aapl" sheetId="28" r:id="rId26"/>
+    <sheet name="mdd_5_tsla" sheetId="29" r:id="rId27"/>
+    <sheet name="calmar_5_tsla" sheetId="30" r:id="rId28"/>
+    <sheet name="alpha_5_tsla_sp500_rf" sheetId="31" r:id="rId29"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">adx_5_tsla!$A$1:$AH$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -59,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="123">
   <si>
     <t>close</t>
   </si>
@@ -320,6 +325,114 @@
   </si>
   <si>
     <t>avg vol</t>
+  </si>
+  <si>
+    <t>TSLA</t>
+  </si>
+  <si>
+    <t>SP500</t>
+  </si>
+  <si>
+    <t>beta_5</t>
+  </si>
+  <si>
+    <t>covar_5</t>
+  </si>
+  <si>
+    <t>var_5</t>
+  </si>
+  <si>
+    <t>slope(mr, br)</t>
+  </si>
+  <si>
+    <t>sqrt(252)</t>
+  </si>
+  <si>
+    <t>threshold</t>
+  </si>
+  <si>
+    <t>pct_change - threshold</t>
+  </si>
+  <si>
+    <t>square</t>
+  </si>
+  <si>
+    <t>downside_deviation_2</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>AAPL</t>
+  </si>
+  <si>
+    <t>rf</t>
+  </si>
+  <si>
+    <t>RF</t>
+  </si>
+  <si>
+    <t>rf daily</t>
+  </si>
+  <si>
+    <t>excess</t>
+  </si>
+  <si>
+    <t>mean_excess</t>
+  </si>
+  <si>
+    <t>mean_stddev</t>
+  </si>
+  <si>
+    <t>sharpe</t>
+  </si>
+  <si>
+    <t>roll_max</t>
+  </si>
+  <si>
+    <t>drawdown</t>
+  </si>
+  <si>
+    <t>mdd</t>
+  </si>
+  <si>
+    <t>mdd.abs</t>
+  </si>
+  <si>
+    <t>cagr</t>
+  </si>
+  <si>
+    <t>shift(5)</t>
+  </si>
+  <si>
+    <t>calmar</t>
+  </si>
+  <si>
+    <t>benchmark_returns</t>
+  </si>
+  <si>
+    <t>asset_returns</t>
+  </si>
+  <si>
+    <t>beta</t>
+  </si>
+  <si>
+    <t>mean_asset</t>
+  </si>
+  <si>
+    <t>mean_bench</t>
+  </si>
+  <si>
+    <t>mean_rf</t>
+  </si>
+  <si>
+    <t>expected</t>
+  </si>
+  <si>
+    <t>mean</t>
+  </si>
+  <si>
+    <t>median</t>
   </si>
 </sst>
 </file>
@@ -854,7 +967,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -2037,7 +2150,7 @@
         <v>102</v>
       </c>
       <c r="C6" s="2">
-        <f>B2</f>
+        <f t="shared" ref="C6:C16" si="0">B2</f>
         <v>100</v>
       </c>
       <c r="D6" s="10">
@@ -2055,11 +2168,11 @@
         <v>104</v>
       </c>
       <c r="C7" s="2">
-        <f>B3</f>
+        <f t="shared" si="0"/>
         <v>102</v>
       </c>
       <c r="D7" s="10">
-        <f t="shared" ref="D7:D16" si="0">B7-C7</f>
+        <f t="shared" ref="D7:D16" si="1">B7-C7</f>
         <v>2</v>
       </c>
     </row>
@@ -2073,11 +2186,11 @@
         <v>106</v>
       </c>
       <c r="C8" s="2">
-        <f>B4</f>
+        <f t="shared" si="0"/>
         <v>101</v>
       </c>
       <c r="D8" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>5</v>
       </c>
     </row>
@@ -2091,11 +2204,11 @@
         <v>105</v>
       </c>
       <c r="C9" s="2">
-        <f>B5</f>
+        <f t="shared" si="0"/>
         <v>103</v>
       </c>
       <c r="D9" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
     </row>
@@ -2109,11 +2222,11 @@
         <v>107</v>
       </c>
       <c r="C10" s="2">
-        <f>B6</f>
+        <f t="shared" si="0"/>
         <v>102</v>
       </c>
       <c r="D10" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>5</v>
       </c>
     </row>
@@ -2127,11 +2240,11 @@
         <v>108</v>
       </c>
       <c r="C11" s="2">
-        <f>B7</f>
+        <f t="shared" si="0"/>
         <v>104</v>
       </c>
       <c r="D11" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
     </row>
@@ -2145,11 +2258,11 @@
         <v>110</v>
       </c>
       <c r="C12" s="2">
-        <f>B8</f>
+        <f t="shared" si="0"/>
         <v>106</v>
       </c>
       <c r="D12" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
     </row>
@@ -2163,11 +2276,11 @@
         <v>109</v>
       </c>
       <c r="C13" s="2">
-        <f>B9</f>
+        <f t="shared" si="0"/>
         <v>105</v>
       </c>
       <c r="D13" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
     </row>
@@ -2181,11 +2294,11 @@
         <v>111</v>
       </c>
       <c r="C14" s="2">
-        <f>B10</f>
+        <f t="shared" si="0"/>
         <v>107</v>
       </c>
       <c r="D14" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
     </row>
@@ -2199,11 +2312,11 @@
         <v>112</v>
       </c>
       <c r="C15" s="2">
-        <f>B11</f>
+        <f t="shared" si="0"/>
         <v>108</v>
       </c>
       <c r="D15" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
     </row>
@@ -2217,11 +2330,11 @@
         <v>113</v>
       </c>
       <c r="C16" s="2">
-        <f>B12</f>
+        <f t="shared" si="0"/>
         <v>110</v>
       </c>
       <c r="D16" s="10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
     </row>
@@ -2924,7 +3037,7 @@
         <v>105</v>
       </c>
       <c r="D9" s="2">
-        <f t="shared" ref="D7:D11" si="4">STDEV((B5:B9))</f>
+        <f t="shared" ref="D9:D11" si="4">STDEV((B5:B9))</f>
         <v>1.5811388300841898</v>
       </c>
       <c r="E9">
@@ -6990,9 +7103,3238 @@
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB1D2642-5A53-4CED-8743-A895F1EE0638}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:J17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="12.28515625" customWidth="1"/>
+    <col min="2" max="3" width="9.140625" style="2"/>
+    <col min="4" max="6" width="13.42578125" style="10" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.140625" style="10"/>
+    <col min="8" max="8" width="10.7109375" style="10" customWidth="1"/>
+    <col min="9" max="9" width="14" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B1" s="2" t="str">
+        <f>tsla!B1</f>
+        <v>close</v>
+      </c>
+      <c r="C1" s="2" t="str">
+        <f>'sp500'!B1</f>
+        <v>close</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="G1" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="J1" s="10" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
+        <f>tsla!A2</f>
+        <v>45292</v>
+      </c>
+      <c r="B2" s="2">
+        <f>tsla!B2</f>
+        <v>100</v>
+      </c>
+      <c r="C2" s="2">
+        <f>'sp500'!B2</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <f>tsla!A3</f>
+        <v>45293</v>
+      </c>
+      <c r="B3" s="2">
+        <f>tsla!B3</f>
+        <v>102</v>
+      </c>
+      <c r="C3" s="2">
+        <f>'sp500'!B3</f>
+        <v>101</v>
+      </c>
+      <c r="D3" s="10">
+        <f>(B3-B2)/B2</f>
+        <v>0.02</v>
+      </c>
+      <c r="E3" s="10">
+        <f>(C3-C2)/C2</f>
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <f>tsla!A4</f>
+        <v>45294</v>
+      </c>
+      <c r="B4" s="2">
+        <f>tsla!B4</f>
+        <v>101</v>
+      </c>
+      <c r="C4" s="2">
+        <f>'sp500'!B4</f>
+        <v>102</v>
+      </c>
+      <c r="D4" s="10">
+        <f t="shared" ref="D4:D16" si="0">(B4-B3)/B3</f>
+        <v>-9.8039215686274508E-3</v>
+      </c>
+      <c r="E4" s="10">
+        <f t="shared" ref="E4:E16" si="1">(C4-C3)/C3</f>
+        <v>9.9009900990099011E-3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <f>tsla!A5</f>
+        <v>45295</v>
+      </c>
+      <c r="B5" s="2">
+        <f>tsla!B5</f>
+        <v>103</v>
+      </c>
+      <c r="C5" s="2">
+        <f>'sp500'!B5</f>
+        <v>101</v>
+      </c>
+      <c r="D5" s="10">
+        <f t="shared" si="0"/>
+        <v>1.9801980198019802E-2</v>
+      </c>
+      <c r="E5" s="10">
+        <f t="shared" si="1"/>
+        <v>-9.8039215686274508E-3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <f>tsla!A6</f>
+        <v>45296</v>
+      </c>
+      <c r="B6" s="2">
+        <f>tsla!B6</f>
+        <v>102</v>
+      </c>
+      <c r="C6" s="2">
+        <f>'sp500'!B6</f>
+        <v>102</v>
+      </c>
+      <c r="D6" s="10">
+        <f t="shared" si="0"/>
+        <v>-9.7087378640776691E-3</v>
+      </c>
+      <c r="E6" s="10">
+        <f t="shared" si="1"/>
+        <v>9.9009900990099011E-3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <f>tsla!A7</f>
+        <v>45297</v>
+      </c>
+      <c r="B7" s="2">
+        <f>tsla!B7</f>
+        <v>104</v>
+      </c>
+      <c r="C7" s="2">
+        <f>'sp500'!B7</f>
+        <v>103</v>
+      </c>
+      <c r="D7" s="10">
+        <f t="shared" si="0"/>
+        <v>1.9607843137254902E-2</v>
+      </c>
+      <c r="E7" s="10">
+        <f t="shared" si="1"/>
+        <v>9.8039215686274508E-3</v>
+      </c>
+      <c r="F7" s="10">
+        <f>_xlfn.COVARIANCE.S(D3:D7, E3:E7)</f>
+        <v>-5.8225212520543568E-5</v>
+      </c>
+      <c r="G7" s="10">
+        <f>VAR(E3:E7)</f>
+        <v>7.7665340346087097E-5</v>
+      </c>
+      <c r="H7" s="10">
+        <f>F7/G7</f>
+        <v>-0.74969365048919212</v>
+      </c>
+      <c r="I7">
+        <f>SLOPE(D3:D7,E3:E7)</f>
+        <v>-0.74969365048919212</v>
+      </c>
+      <c r="J7" s="12">
+        <f>H7-I7</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <f>tsla!A8</f>
+        <v>45298</v>
+      </c>
+      <c r="B8" s="2">
+        <f>tsla!B8</f>
+        <v>106</v>
+      </c>
+      <c r="C8" s="2">
+        <f>'sp500'!B8</f>
+        <v>104</v>
+      </c>
+      <c r="D8" s="10">
+        <f t="shared" si="0"/>
+        <v>1.9230769230769232E-2</v>
+      </c>
+      <c r="E8" s="10">
+        <f t="shared" si="1"/>
+        <v>9.7087378640776691E-3</v>
+      </c>
+      <c r="F8" s="10">
+        <f t="shared" ref="F8:F16" si="2">_xlfn.COVARIANCE.S(D4:D8, E4:E8)</f>
+        <v>-5.9832533897468051E-5</v>
+      </c>
+      <c r="G8" s="10">
+        <f t="shared" ref="G8:G16" si="3">VAR(E4:E8)</f>
+        <v>7.7094015233558885E-5</v>
+      </c>
+      <c r="H8" s="10">
+        <f t="shared" ref="H8:H16" si="4">F8/G8</f>
+        <v>-0.77609829655652773</v>
+      </c>
+      <c r="I8">
+        <f t="shared" ref="I8:I16" si="5">SLOPE(D4:D8,E4:E8)</f>
+        <v>-0.77609829655652762</v>
+      </c>
+      <c r="J8" s="12">
+        <f t="shared" ref="J8:J16" si="6">H8-I8</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <f>tsla!A9</f>
+        <v>45299</v>
+      </c>
+      <c r="B9" s="2">
+        <f>tsla!B9</f>
+        <v>105</v>
+      </c>
+      <c r="C9" s="2">
+        <f>'sp500'!B9</f>
+        <v>103</v>
+      </c>
+      <c r="D9" s="10">
+        <f t="shared" si="0"/>
+        <v>-9.433962264150943E-3</v>
+      </c>
+      <c r="E9" s="10">
+        <f t="shared" si="1"/>
+        <v>-9.6153846153846159E-3</v>
+      </c>
+      <c r="F9" s="10">
+        <f t="shared" si="2"/>
+        <v>2.5109287828173313E-5</v>
+      </c>
+      <c r="G9" s="10">
+        <f t="shared" si="3"/>
+        <v>1.1425029840327122E-4</v>
+      </c>
+      <c r="H9" s="10">
+        <f t="shared" si="4"/>
+        <v>0.2197743741512572</v>
+      </c>
+      <c r="I9">
+        <f t="shared" si="5"/>
+        <v>0.21977437415125722</v>
+      </c>
+      <c r="J9" s="12">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <f>tsla!A10</f>
+        <v>45300</v>
+      </c>
+      <c r="B10" s="2">
+        <f>tsla!B10</f>
+        <v>107</v>
+      </c>
+      <c r="C10" s="2">
+        <f>'sp500'!B10</f>
+        <v>104</v>
+      </c>
+      <c r="D10" s="10">
+        <f t="shared" si="0"/>
+        <v>1.9047619047619049E-2</v>
+      </c>
+      <c r="E10" s="10">
+        <f t="shared" si="1"/>
+        <v>9.7087378640776691E-3</v>
+      </c>
+      <c r="F10" s="10">
+        <f t="shared" si="2"/>
+        <v>8.2453138742114712E-5</v>
+      </c>
+      <c r="G10" s="10">
+        <f t="shared" si="3"/>
+        <v>7.5247160894103656E-5</v>
+      </c>
+      <c r="H10" s="10">
+        <f t="shared" si="4"/>
+        <v>1.0957641160462137</v>
+      </c>
+      <c r="I10">
+        <f t="shared" si="5"/>
+        <v>1.0957641160462135</v>
+      </c>
+      <c r="J10" s="12">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <f>tsla!A11</f>
+        <v>45301</v>
+      </c>
+      <c r="B11" s="2">
+        <f>tsla!B11</f>
+        <v>108</v>
+      </c>
+      <c r="C11" s="2">
+        <f>'sp500'!B11</f>
+        <v>104</v>
+      </c>
+      <c r="D11" s="10">
+        <f t="shared" si="0"/>
+        <v>9.3457943925233638E-3</v>
+      </c>
+      <c r="E11" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F11" s="10">
+        <f t="shared" si="2"/>
+        <v>1.0698546403946069E-4</v>
+      </c>
+      <c r="G11" s="10">
+        <f t="shared" si="3"/>
+        <v>7.5053133649923839E-5</v>
+      </c>
+      <c r="H11" s="10">
+        <f t="shared" si="4"/>
+        <v>1.4254629865087485</v>
+      </c>
+      <c r="I11">
+        <f t="shared" si="5"/>
+        <v>1.4254629865087485</v>
+      </c>
+      <c r="J11" s="12">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
+        <f>tsla!A12</f>
+        <v>45302</v>
+      </c>
+      <c r="B12" s="2">
+        <f>tsla!B12</f>
+        <v>110</v>
+      </c>
+      <c r="C12" s="2">
+        <f>'sp500'!B12</f>
+        <v>105</v>
+      </c>
+      <c r="D12" s="10">
+        <f t="shared" si="0"/>
+        <v>1.8518518518518517E-2</v>
+      </c>
+      <c r="E12" s="10">
+        <f t="shared" si="1"/>
+        <v>9.6153846153846159E-3</v>
+      </c>
+      <c r="F12" s="10">
+        <f t="shared" si="2"/>
+        <v>1.0504514475064694E-4</v>
+      </c>
+      <c r="G12" s="10">
+        <f t="shared" si="3"/>
+        <v>7.4505687924900196E-5</v>
+      </c>
+      <c r="H12" s="10">
+        <f t="shared" si="4"/>
+        <v>1.4098943003724727</v>
+      </c>
+      <c r="I12">
+        <f t="shared" si="5"/>
+        <v>1.4098943003724727</v>
+      </c>
+      <c r="J12" s="12">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
+        <f>tsla!A13</f>
+        <v>45303</v>
+      </c>
+      <c r="B13" s="2">
+        <f>tsla!B13</f>
+        <v>109</v>
+      </c>
+      <c r="C13" s="2">
+        <f>'sp500'!B13</f>
+        <v>105</v>
+      </c>
+      <c r="D13" s="10">
+        <f t="shared" si="0"/>
+        <v>-9.0909090909090905E-3</v>
+      </c>
+      <c r="E13" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F13" s="10">
+        <f t="shared" si="2"/>
+        <v>9.9645421980312657E-5</v>
+      </c>
+      <c r="G13" s="10">
+        <f t="shared" si="3"/>
+        <v>6.5079728833562667E-5</v>
+      </c>
+      <c r="H13" s="10">
+        <f t="shared" si="4"/>
+        <v>1.5311284138129952</v>
+      </c>
+      <c r="I13">
+        <f t="shared" si="5"/>
+        <v>1.5311284138129952</v>
+      </c>
+      <c r="J13" s="12">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
+        <f>tsla!A14</f>
+        <v>45304</v>
+      </c>
+      <c r="B14" s="2">
+        <f>tsla!B14</f>
+        <v>111</v>
+      </c>
+      <c r="C14" s="2">
+        <f>'sp500'!B14</f>
+        <v>106</v>
+      </c>
+      <c r="D14" s="10">
+        <f t="shared" si="0"/>
+        <v>1.834862385321101E-2</v>
+      </c>
+      <c r="E14" s="10">
+        <f t="shared" si="1"/>
+        <v>9.5238095238095247E-3</v>
+      </c>
+      <c r="F14" s="10">
+        <f t="shared" si="2"/>
+        <v>5.3416046770501661E-5</v>
+      </c>
+      <c r="G14" s="10">
+        <f t="shared" si="3"/>
+        <v>2.7744380971969199E-5</v>
+      </c>
+      <c r="H14" s="10">
+        <f t="shared" si="4"/>
+        <v>1.9252924339695721</v>
+      </c>
+      <c r="I14">
+        <f t="shared" si="5"/>
+        <v>1.9252924339695721</v>
+      </c>
+      <c r="J14" s="12">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
+        <f>tsla!A15</f>
+        <v>45305</v>
+      </c>
+      <c r="B15" s="2">
+        <f>tsla!B15</f>
+        <v>112</v>
+      </c>
+      <c r="C15" s="2">
+        <f>'sp500'!B15</f>
+        <v>106</v>
+      </c>
+      <c r="D15" s="10">
+        <f t="shared" si="0"/>
+        <v>9.0090090090090089E-3</v>
+      </c>
+      <c r="E15" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F15" s="10">
+        <f t="shared" si="2"/>
+        <v>4.4057325820880084E-5</v>
+      </c>
+      <c r="G15" s="10">
+        <f t="shared" si="3"/>
+        <v>2.7474204672006873E-5</v>
+      </c>
+      <c r="H15" s="10">
+        <f t="shared" si="4"/>
+        <v>1.6035887606882957</v>
+      </c>
+      <c r="I15">
+        <f t="shared" si="5"/>
+        <v>1.6035887606882955</v>
+      </c>
+      <c r="J15" s="12">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
+        <f>tsla!A16</f>
+        <v>45306</v>
+      </c>
+      <c r="B16" s="2">
+        <f>tsla!B16</f>
+        <v>113</v>
+      </c>
+      <c r="C16" s="2">
+        <f>'sp500'!B16</f>
+        <v>107</v>
+      </c>
+      <c r="D16" s="10">
+        <f t="shared" si="0"/>
+        <v>8.9285714285714281E-3</v>
+      </c>
+      <c r="E16" s="10">
+        <f>(C16-C15)/C15</f>
+        <v>9.433962264150943E-3</v>
+      </c>
+      <c r="F16" s="10">
+        <f t="shared" si="2"/>
+        <v>4.3951423190189197E-5</v>
+      </c>
+      <c r="G16" s="10">
+        <f t="shared" si="3"/>
+        <v>2.7218289944750036E-5</v>
+      </c>
+      <c r="H16" s="10">
+        <f t="shared" si="4"/>
+        <v>1.6147753323006506</v>
+      </c>
+      <c r="I16">
+        <f t="shared" si="5"/>
+        <v>1.6147753323006508</v>
+      </c>
+      <c r="J16" s="12">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B17" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="D17" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="E17" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="G17" s="10" t="s">
+        <v>88</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9563DECA-6B64-44B8-95EE-69AC8690688C}">
+  <dimension ref="A1:F11"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="14.5703125" customWidth="1"/>
+    <col min="3" max="3" width="12.85546875" style="10" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.140625" style="12"/>
+    <col min="5" max="5" width="10.140625" style="12" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.140625" style="12"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="E1" s="12" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
+        <f>aapl!A2</f>
+        <v>45292</v>
+      </c>
+      <c r="B2" s="2">
+        <f>aapl!B2</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <f>A2+1</f>
+        <v>45293</v>
+      </c>
+      <c r="B3" s="2">
+        <f>aapl!B3</f>
+        <v>101</v>
+      </c>
+      <c r="C3" s="10">
+        <f>(B3-B2)/B2</f>
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <f t="shared" ref="A4:A11" si="0">A3+1</f>
+        <v>45294</v>
+      </c>
+      <c r="B4" s="2">
+        <f>aapl!B4</f>
+        <v>102</v>
+      </c>
+      <c r="C4" s="10">
+        <f t="shared" ref="C4:C11" si="1">(B4-B3)/B3</f>
+        <v>9.9009900990099011E-3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <f t="shared" si="0"/>
+        <v>45295</v>
+      </c>
+      <c r="B5" s="2">
+        <f>aapl!B5</f>
+        <v>103</v>
+      </c>
+      <c r="C5" s="10">
+        <f t="shared" si="1"/>
+        <v>9.8039215686274508E-3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <f t="shared" si="0"/>
+        <v>45296</v>
+      </c>
+      <c r="B6" s="2">
+        <f>aapl!B6</f>
+        <v>104</v>
+      </c>
+      <c r="C6" s="10">
+        <f t="shared" si="1"/>
+        <v>9.7087378640776691E-3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <f t="shared" si="0"/>
+        <v>45297</v>
+      </c>
+      <c r="B7" s="2">
+        <f>aapl!B7</f>
+        <v>105</v>
+      </c>
+      <c r="C7" s="10">
+        <f t="shared" si="1"/>
+        <v>9.6153846153846159E-3</v>
+      </c>
+      <c r="D7" s="12">
+        <f>STDEV(C3:C7)</f>
+        <v>1.5203404236285457E-4</v>
+      </c>
+      <c r="E7" s="12">
+        <f>SQRT(252)</f>
+        <v>15.874507866387544</v>
+      </c>
+      <c r="F7" s="12">
+        <f>D7*E7</f>
+        <v>2.4134656014478321E-3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <f t="shared" si="0"/>
+        <v>45298</v>
+      </c>
+      <c r="B8" s="2">
+        <f>aapl!B8</f>
+        <v>106</v>
+      </c>
+      <c r="C8" s="10">
+        <f t="shared" si="1"/>
+        <v>9.5238095238095247E-3</v>
+      </c>
+      <c r="D8" s="12">
+        <f t="shared" ref="D8:D11" si="2">STDEV(C4:C8)</f>
+        <v>1.4909511988781216E-4</v>
+      </c>
+      <c r="E8" s="12">
+        <f t="shared" ref="E8:E11" si="3">SQRT(252)</f>
+        <v>15.874507866387544</v>
+      </c>
+      <c r="F8" s="12">
+        <f t="shared" ref="F8:F11" si="4">D8*E8</f>
+        <v>2.3668116534990681E-3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <f t="shared" si="0"/>
+        <v>45299</v>
+      </c>
+      <c r="B9" s="2">
+        <f>aapl!B9</f>
+        <v>107</v>
+      </c>
+      <c r="C9" s="10">
+        <f t="shared" si="1"/>
+        <v>9.433962264150943E-3</v>
+      </c>
+      <c r="D9" s="12">
+        <f t="shared" si="2"/>
+        <v>1.462406086478717E-4</v>
+      </c>
+      <c r="E9" s="12">
+        <f t="shared" si="3"/>
+        <v>15.874507866387544</v>
+      </c>
+      <c r="F9" s="12">
+        <f t="shared" si="4"/>
+        <v>2.3214976923659415E-3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <f t="shared" si="0"/>
+        <v>45300</v>
+      </c>
+      <c r="B10" s="2">
+        <f>aapl!B10</f>
+        <v>108</v>
+      </c>
+      <c r="C10" s="10">
+        <f t="shared" si="1"/>
+        <v>9.3457943925233638E-3</v>
+      </c>
+      <c r="D10" s="12">
+        <f t="shared" si="2"/>
+        <v>1.4346730633557313E-4</v>
+      </c>
+      <c r="E10" s="12">
+        <f t="shared" si="3"/>
+        <v>15.874507866387544</v>
+      </c>
+      <c r="F10" s="12">
+        <f t="shared" si="4"/>
+        <v>2.2774728829934874E-3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <f t="shared" si="0"/>
+        <v>45301</v>
+      </c>
+      <c r="B11" s="2">
+        <f>aapl!B11</f>
+        <v>109</v>
+      </c>
+      <c r="C11" s="10">
+        <f t="shared" si="1"/>
+        <v>9.2592592592592587E-3</v>
+      </c>
+      <c r="D11" s="12">
+        <f t="shared" si="2"/>
+        <v>1.4077216109108567E-4</v>
+      </c>
+      <c r="E11" s="12">
+        <f t="shared" si="3"/>
+        <v>15.874507866387544</v>
+      </c>
+      <c r="F11" s="12">
+        <f t="shared" si="4"/>
+        <v>2.234688778608814E-3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F57B53C-CDEC-4445-AFC4-B6CF897EC761}">
+  <dimension ref="A1:G19"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="11.7109375" customWidth="1"/>
+    <col min="3" max="3" width="13.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.42578125" style="2" customWidth="1"/>
+    <col min="6" max="6" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="20.7109375" style="10" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B1" s="2" t="str">
+        <f>tsla!B1</f>
+        <v>close</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="G1" s="10" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
+        <f>tsla!A2</f>
+        <v>45292</v>
+      </c>
+      <c r="B2" s="2">
+        <f>tsla!B2</f>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <f>tsla!A3</f>
+        <v>45293</v>
+      </c>
+      <c r="B3" s="2">
+        <f>tsla!B3</f>
+        <v>102</v>
+      </c>
+      <c r="C3" s="2">
+        <f>(B3-B2)/B2</f>
+        <v>0.02</v>
+      </c>
+      <c r="D3" s="2">
+        <f>C3-$D$19</f>
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <f>tsla!A4</f>
+        <v>45294</v>
+      </c>
+      <c r="B4" s="2">
+        <f>tsla!B4</f>
+        <v>101</v>
+      </c>
+      <c r="C4" s="2">
+        <f t="shared" ref="C4:C16" si="0">(B4-B3)/B3</f>
+        <v>-9.8039215686274508E-3</v>
+      </c>
+      <c r="D4" s="2">
+        <f t="shared" ref="D4:D16" si="1">C4-$D$19</f>
+        <v>-9.8039215686274508E-3</v>
+      </c>
+      <c r="E4" s="2">
+        <f t="shared" ref="E4:E16" si="2">IF(D4&lt;0,D4^2,D4)</f>
+        <v>9.6116878123798542E-5</v>
+      </c>
+      <c r="G4" s="10" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <f>tsla!A5</f>
+        <v>45295</v>
+      </c>
+      <c r="B5" s="2">
+        <f>tsla!B5</f>
+        <v>103</v>
+      </c>
+      <c r="C5" s="2">
+        <f t="shared" si="0"/>
+        <v>1.9801980198019802E-2</v>
+      </c>
+      <c r="D5" s="2">
+        <f t="shared" si="1"/>
+        <v>1.9801980198019802E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <f>tsla!A6</f>
+        <v>45296</v>
+      </c>
+      <c r="B6" s="2">
+        <f>tsla!B6</f>
+        <v>102</v>
+      </c>
+      <c r="C6" s="2">
+        <f t="shared" si="0"/>
+        <v>-9.7087378640776691E-3</v>
+      </c>
+      <c r="D6" s="2">
+        <f t="shared" si="1"/>
+        <v>-9.7087378640776691E-3</v>
+      </c>
+      <c r="E6" s="2">
+        <f t="shared" si="2"/>
+        <v>9.4259590913375421E-5</v>
+      </c>
+      <c r="F6">
+        <f>AVERAGE(E4:E6)*252</f>
+        <v>2.398743509868392E-2</v>
+      </c>
+      <c r="G6" s="10">
+        <f>SQRT(F6)</f>
+        <v>0.15487877549452642</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <f>tsla!A7</f>
+        <v>45297</v>
+      </c>
+      <c r="B7" s="2">
+        <f>tsla!B7</f>
+        <v>104</v>
+      </c>
+      <c r="C7" s="2">
+        <f t="shared" si="0"/>
+        <v>1.9607843137254902E-2</v>
+      </c>
+      <c r="D7" s="2">
+        <f t="shared" si="1"/>
+        <v>1.9607843137254902E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <f>tsla!A8</f>
+        <v>45298</v>
+      </c>
+      <c r="B8" s="2">
+        <f>tsla!B8</f>
+        <v>106</v>
+      </c>
+      <c r="C8" s="2">
+        <f t="shared" si="0"/>
+        <v>1.9230769230769232E-2</v>
+      </c>
+      <c r="D8" s="2">
+        <f t="shared" si="1"/>
+        <v>1.9230769230769232E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <f>tsla!A9</f>
+        <v>45299</v>
+      </c>
+      <c r="B9" s="2">
+        <f>tsla!B9</f>
+        <v>105</v>
+      </c>
+      <c r="C9" s="2">
+        <f t="shared" si="0"/>
+        <v>-9.433962264150943E-3</v>
+      </c>
+      <c r="D9" s="2">
+        <f t="shared" si="1"/>
+        <v>-9.433962264150943E-3</v>
+      </c>
+      <c r="E9" s="2">
+        <f t="shared" si="2"/>
+        <v>8.8999644001423986E-5</v>
+      </c>
+      <c r="F9">
+        <f>AVERAGE(E6:E9)*252</f>
+        <v>2.3090663599264726E-2</v>
+      </c>
+      <c r="G9" s="10">
+        <f t="shared" ref="G8:G16" si="3">SQRT(F9)</f>
+        <v>0.15195612392814159</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <f>tsla!A10</f>
+        <v>45300</v>
+      </c>
+      <c r="B10" s="2">
+        <f>tsla!B10</f>
+        <v>107</v>
+      </c>
+      <c r="C10" s="2">
+        <f t="shared" si="0"/>
+        <v>1.9047619047619049E-2</v>
+      </c>
+      <c r="D10" s="2">
+        <f t="shared" si="1"/>
+        <v>1.9047619047619049E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <f>tsla!A11</f>
+        <v>45301</v>
+      </c>
+      <c r="B11" s="2">
+        <f>tsla!B11</f>
+        <v>108</v>
+      </c>
+      <c r="C11" s="2">
+        <f t="shared" si="0"/>
+        <v>9.3457943925233638E-3</v>
+      </c>
+      <c r="D11" s="2">
+        <f t="shared" si="1"/>
+        <v>9.3457943925233638E-3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
+        <f>tsla!A12</f>
+        <v>45302</v>
+      </c>
+      <c r="B12" s="2">
+        <f>tsla!B12</f>
+        <v>110</v>
+      </c>
+      <c r="C12" s="2">
+        <f t="shared" si="0"/>
+        <v>1.8518518518518517E-2</v>
+      </c>
+      <c r="D12" s="2">
+        <f t="shared" si="1"/>
+        <v>1.8518518518518517E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
+        <f>tsla!A13</f>
+        <v>45303</v>
+      </c>
+      <c r="B13" s="2">
+        <f>tsla!B13</f>
+        <v>109</v>
+      </c>
+      <c r="C13" s="2">
+        <f t="shared" si="0"/>
+        <v>-9.0909090909090905E-3</v>
+      </c>
+      <c r="D13" s="2">
+        <f t="shared" si="1"/>
+        <v>-9.0909090909090905E-3</v>
+      </c>
+      <c r="E13" s="2">
+        <f t="shared" si="2"/>
+        <v>8.2644628099173546E-5</v>
+      </c>
+      <c r="F13">
+        <f>AVERAGE(E9:E13)*252</f>
+        <v>2.1627178284675287E-2</v>
+      </c>
+      <c r="G13" s="10">
+        <f t="shared" si="3"/>
+        <v>0.14706181790211656</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
+        <f>tsla!A14</f>
+        <v>45304</v>
+      </c>
+      <c r="B14" s="2">
+        <f>tsla!B14</f>
+        <v>111</v>
+      </c>
+      <c r="C14" s="2">
+        <f t="shared" si="0"/>
+        <v>1.834862385321101E-2</v>
+      </c>
+      <c r="D14" s="2">
+        <f t="shared" si="1"/>
+        <v>1.834862385321101E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
+        <f>tsla!A15</f>
+        <v>45305</v>
+      </c>
+      <c r="B15" s="2">
+        <f>tsla!B15</f>
+        <v>112</v>
+      </c>
+      <c r="C15" s="2">
+        <f t="shared" si="0"/>
+        <v>9.0090090090090089E-3</v>
+      </c>
+      <c r="D15" s="2">
+        <f t="shared" si="1"/>
+        <v>9.0090090090090089E-3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
+        <f>tsla!A16</f>
+        <v>45306</v>
+      </c>
+      <c r="B16" s="2">
+        <f>tsla!B16</f>
+        <v>113</v>
+      </c>
+      <c r="C16" s="2">
+        <f t="shared" si="0"/>
+        <v>8.9285714285714281E-3</v>
+      </c>
+      <c r="D16" s="2">
+        <f t="shared" si="1"/>
+        <v>8.9285714285714281E-3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B17" s="2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>94</v>
+      </c>
+      <c r="D19" s="2">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C55FBD1-C46D-444C-AC2C-007480E92271}">
+  <dimension ref="A1:I12"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="12.5703125" customWidth="1"/>
+    <col min="3" max="3" width="9.140625" style="2"/>
+    <col min="4" max="4" width="11.42578125" style="10" customWidth="1"/>
+    <col min="5" max="5" width="9.140625" style="10"/>
+    <col min="6" max="6" width="9.140625" style="2"/>
+    <col min="7" max="7" width="12.7109375" style="2" customWidth="1"/>
+    <col min="8" max="8" width="13.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.5703125" style="10" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
+        <f>aapl!A2</f>
+        <v>45292</v>
+      </c>
+      <c r="B2" s="2">
+        <f>aapl!B2</f>
+        <v>100</v>
+      </c>
+      <c r="C2" s="2">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <f>A2+1</f>
+        <v>45293</v>
+      </c>
+      <c r="B3" s="2">
+        <f>aapl!B3</f>
+        <v>101</v>
+      </c>
+      <c r="C3" s="2">
+        <f>C2</f>
+        <v>0.04</v>
+      </c>
+      <c r="D3" s="10">
+        <f>(B3-B2)/B2</f>
+        <v>0.01</v>
+      </c>
+      <c r="E3" s="10">
+        <f>((1+C3)^(1/252)) - 1</f>
+        <v>1.5564986279126281E-4</v>
+      </c>
+      <c r="F3" s="10">
+        <f>D3-E3</f>
+        <v>9.8443501372087374E-3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <f t="shared" ref="A4:A11" si="0">A3+1</f>
+        <v>45294</v>
+      </c>
+      <c r="B4" s="2">
+        <f>aapl!B4</f>
+        <v>102</v>
+      </c>
+      <c r="C4" s="2">
+        <f t="shared" ref="C4:C11" si="1">C3</f>
+        <v>0.04</v>
+      </c>
+      <c r="D4" s="10">
+        <f t="shared" ref="D4:D11" si="2">(B4-B3)/B3</f>
+        <v>9.9009900990099011E-3</v>
+      </c>
+      <c r="E4" s="10">
+        <f t="shared" ref="E4:E11" si="3">((1+C4)^(1/252)) - 1</f>
+        <v>1.5564986279126281E-4</v>
+      </c>
+      <c r="F4" s="10">
+        <f t="shared" ref="F4:F11" si="4">D4-E4</f>
+        <v>9.7453402362186383E-3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <f t="shared" si="0"/>
+        <v>45295</v>
+      </c>
+      <c r="B5" s="2">
+        <f>aapl!B5</f>
+        <v>103</v>
+      </c>
+      <c r="C5" s="2">
+        <f t="shared" si="1"/>
+        <v>0.04</v>
+      </c>
+      <c r="D5" s="10">
+        <f t="shared" si="2"/>
+        <v>9.8039215686274508E-3</v>
+      </c>
+      <c r="E5" s="10">
+        <f t="shared" si="3"/>
+        <v>1.5564986279126281E-4</v>
+      </c>
+      <c r="F5" s="10">
+        <f t="shared" si="4"/>
+        <v>9.648271705836188E-3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <f t="shared" si="0"/>
+        <v>45296</v>
+      </c>
+      <c r="B6" s="2">
+        <f>aapl!B6</f>
+        <v>104</v>
+      </c>
+      <c r="C6" s="2">
+        <f t="shared" si="1"/>
+        <v>0.04</v>
+      </c>
+      <c r="D6" s="10">
+        <f t="shared" si="2"/>
+        <v>9.7087378640776691E-3</v>
+      </c>
+      <c r="E6" s="10">
+        <f t="shared" si="3"/>
+        <v>1.5564986279126281E-4</v>
+      </c>
+      <c r="F6" s="10">
+        <f t="shared" si="4"/>
+        <v>9.5530880012864063E-3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <f t="shared" si="0"/>
+        <v>45297</v>
+      </c>
+      <c r="B7" s="2">
+        <f>aapl!B7</f>
+        <v>105</v>
+      </c>
+      <c r="C7" s="2">
+        <f t="shared" si="1"/>
+        <v>0.04</v>
+      </c>
+      <c r="D7" s="10">
+        <f t="shared" si="2"/>
+        <v>9.6153846153846159E-3</v>
+      </c>
+      <c r="E7" s="10">
+        <f t="shared" si="3"/>
+        <v>1.5564986279126281E-4</v>
+      </c>
+      <c r="F7" s="10">
+        <f t="shared" si="4"/>
+        <v>9.4597347525933531E-3</v>
+      </c>
+      <c r="G7" s="10">
+        <f>AVERAGE(F3:F7)</f>
+        <v>9.6501569666286643E-3</v>
+      </c>
+      <c r="H7" s="2">
+        <f>STDEV(F3:F7)</f>
+        <v>1.5203404236285457E-4</v>
+      </c>
+      <c r="I7" s="10">
+        <f>(G7/H7)*SQRT(252)</f>
+        <v>1007.6130996570115</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <f t="shared" si="0"/>
+        <v>45298</v>
+      </c>
+      <c r="B8" s="2">
+        <f>aapl!B8</f>
+        <v>106</v>
+      </c>
+      <c r="C8" s="2">
+        <f t="shared" si="1"/>
+        <v>0.04</v>
+      </c>
+      <c r="D8" s="10">
+        <f t="shared" si="2"/>
+        <v>9.5238095238095247E-3</v>
+      </c>
+      <c r="E8" s="10">
+        <f t="shared" si="3"/>
+        <v>1.5564986279126281E-4</v>
+      </c>
+      <c r="F8" s="10">
+        <f t="shared" si="4"/>
+        <v>9.3681596610182619E-3</v>
+      </c>
+      <c r="G8" s="10">
+        <f t="shared" ref="G8:G11" si="5">AVERAGE(F4:F8)</f>
+        <v>9.5549188713905699E-3</v>
+      </c>
+      <c r="H8" s="2">
+        <f t="shared" ref="H8:H11" si="6">STDEV(F4:F8)</f>
+        <v>1.4909511988781216E-4</v>
+      </c>
+      <c r="I8" s="10">
+        <f t="shared" ref="I8:I11" si="7">(G8/H8)*SQRT(252)</f>
+        <v>1017.3346713206776</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <f t="shared" si="0"/>
+        <v>45299</v>
+      </c>
+      <c r="B9" s="2">
+        <f>aapl!B9</f>
+        <v>107</v>
+      </c>
+      <c r="C9" s="2">
+        <f t="shared" si="1"/>
+        <v>0.04</v>
+      </c>
+      <c r="D9" s="10">
+        <f t="shared" si="2"/>
+        <v>9.433962264150943E-3</v>
+      </c>
+      <c r="E9" s="10">
+        <f t="shared" si="3"/>
+        <v>1.5564986279126281E-4</v>
+      </c>
+      <c r="F9" s="10">
+        <f t="shared" si="4"/>
+        <v>9.2783124013596802E-3</v>
+      </c>
+      <c r="G9" s="10">
+        <f t="shared" si="5"/>
+        <v>9.4615133044187779E-3</v>
+      </c>
+      <c r="H9" s="2">
+        <f t="shared" si="6"/>
+        <v>1.462406086478717E-4</v>
+      </c>
+      <c r="I9" s="10">
+        <f t="shared" si="7"/>
+        <v>1027.0530789473173</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <f t="shared" si="0"/>
+        <v>45300</v>
+      </c>
+      <c r="B10" s="2">
+        <f>aapl!B10</f>
+        <v>108</v>
+      </c>
+      <c r="C10" s="2">
+        <f t="shared" si="1"/>
+        <v>0.04</v>
+      </c>
+      <c r="D10" s="10">
+        <f t="shared" si="2"/>
+        <v>9.3457943925233638E-3</v>
+      </c>
+      <c r="E10" s="10">
+        <f t="shared" si="3"/>
+        <v>1.5564986279126281E-4</v>
+      </c>
+      <c r="F10" s="10">
+        <f t="shared" si="4"/>
+        <v>9.190144529732101E-3</v>
+      </c>
+      <c r="G10" s="10">
+        <f t="shared" si="5"/>
+        <v>9.3698878691979605E-3</v>
+      </c>
+      <c r="H10" s="2">
+        <f t="shared" si="6"/>
+        <v>1.4346730633557313E-4</v>
+      </c>
+      <c r="I10" s="10">
+        <f t="shared" si="7"/>
+        <v>1036.7683236405142</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <f t="shared" si="0"/>
+        <v>45301</v>
+      </c>
+      <c r="B11" s="2">
+        <f>aapl!B11</f>
+        <v>109</v>
+      </c>
+      <c r="C11" s="2">
+        <f t="shared" si="1"/>
+        <v>0.04</v>
+      </c>
+      <c r="D11" s="10">
+        <f t="shared" si="2"/>
+        <v>9.2592592592592587E-3</v>
+      </c>
+      <c r="E11" s="10">
+        <f t="shared" si="3"/>
+        <v>1.5564986279126281E-4</v>
+      </c>
+      <c r="F11" s="10">
+        <f t="shared" si="4"/>
+        <v>9.1036093964679959E-3</v>
+      </c>
+      <c r="G11" s="10">
+        <f t="shared" si="5"/>
+        <v>9.2799921482342781E-3</v>
+      </c>
+      <c r="H11" s="2">
+        <f t="shared" si="6"/>
+        <v>1.4077216109108567E-4</v>
+      </c>
+      <c r="I11" s="10">
+        <f t="shared" si="7"/>
+        <v>1046.4804064621862</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B12" t="s">
+        <v>99</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00893E21-2836-4B73-8316-4CF03B817790}">
+  <dimension ref="A1:E17"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="13" customWidth="1"/>
+    <col min="3" max="3" width="9.140625" style="2"/>
+    <col min="4" max="4" width="10.85546875" style="12" customWidth="1"/>
+    <col min="5" max="5" width="10.85546875" style="10" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B1" s="2" t="str">
+        <f>tsla!B1</f>
+        <v>close</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="D1" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
+        <f>tsla!A2</f>
+        <v>45292</v>
+      </c>
+      <c r="B2" s="2">
+        <f>tsla!B2</f>
+        <v>100</v>
+      </c>
+      <c r="C2" s="2">
+        <f>B2</f>
+        <v>100</v>
+      </c>
+      <c r="D2" s="12">
+        <f t="shared" ref="D2:D5" si="0">B2/C2 - 1</f>
+        <v>0</v>
+      </c>
+      <c r="E2" s="10">
+        <f>D2</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <f>tsla!A3</f>
+        <v>45293</v>
+      </c>
+      <c r="B3" s="2">
+        <f>tsla!B3</f>
+        <v>102</v>
+      </c>
+      <c r="C3" s="2">
+        <f>MAX(B2:B3)</f>
+        <v>102</v>
+      </c>
+      <c r="D3" s="12">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E3" s="10">
+        <f>MIN(D2:D3)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <f>tsla!A4</f>
+        <v>45294</v>
+      </c>
+      <c r="B4" s="2">
+        <f>tsla!B4</f>
+        <v>101</v>
+      </c>
+      <c r="C4" s="2">
+        <f>MAX(B2:B4)</f>
+        <v>102</v>
+      </c>
+      <c r="D4" s="12">
+        <f t="shared" si="0"/>
+        <v>-9.8039215686274161E-3</v>
+      </c>
+      <c r="E4" s="10">
+        <f>MIN(D2:D4)</f>
+        <v>-9.8039215686274161E-3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <f>tsla!A5</f>
+        <v>45295</v>
+      </c>
+      <c r="B5" s="2">
+        <f>tsla!B5</f>
+        <v>103</v>
+      </c>
+      <c r="C5" s="2">
+        <f>MAX(B2:B5)</f>
+        <v>103</v>
+      </c>
+      <c r="D5" s="12">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="E5" s="10">
+        <f>MIN(D2:D5)</f>
+        <v>-9.8039215686274161E-3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <f>tsla!A6</f>
+        <v>45296</v>
+      </c>
+      <c r="B6" s="2">
+        <f>tsla!B6</f>
+        <v>102</v>
+      </c>
+      <c r="C6" s="2">
+        <f>MAX(B2:B6)</f>
+        <v>103</v>
+      </c>
+      <c r="D6" s="12">
+        <f>B6/C6 - 1</f>
+        <v>-9.7087378640776656E-3</v>
+      </c>
+      <c r="E6" s="10">
+        <f>MIN(D2:D6)</f>
+        <v>-9.8039215686274161E-3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <f>tsla!A7</f>
+        <v>45297</v>
+      </c>
+      <c r="B7" s="2">
+        <f>tsla!B7</f>
+        <v>104</v>
+      </c>
+      <c r="C7" s="2">
+        <f t="shared" ref="C7:C16" si="1">MAX(B3:B7)</f>
+        <v>104</v>
+      </c>
+      <c r="D7" s="12">
+        <f t="shared" ref="D7:D16" si="2">B7/C7 - 1</f>
+        <v>0</v>
+      </c>
+      <c r="E7" s="10">
+        <f t="shared" ref="E7:E16" si="3">MIN(D3:D7)</f>
+        <v>-9.8039215686274161E-3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <f>tsla!A8</f>
+        <v>45298</v>
+      </c>
+      <c r="B8" s="2">
+        <f>tsla!B8</f>
+        <v>106</v>
+      </c>
+      <c r="C8" s="2">
+        <f t="shared" si="1"/>
+        <v>106</v>
+      </c>
+      <c r="D8" s="12">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E8" s="10">
+        <f t="shared" si="3"/>
+        <v>-9.8039215686274161E-3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <f>tsla!A9</f>
+        <v>45299</v>
+      </c>
+      <c r="B9" s="2">
+        <f>tsla!B9</f>
+        <v>105</v>
+      </c>
+      <c r="C9" s="2">
+        <f t="shared" si="1"/>
+        <v>106</v>
+      </c>
+      <c r="D9" s="12">
+        <f t="shared" si="2"/>
+        <v>-9.4339622641509413E-3</v>
+      </c>
+      <c r="E9" s="10">
+        <f t="shared" si="3"/>
+        <v>-9.7087378640776656E-3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <f>tsla!A10</f>
+        <v>45300</v>
+      </c>
+      <c r="B10" s="2">
+        <f>tsla!B10</f>
+        <v>107</v>
+      </c>
+      <c r="C10" s="2">
+        <f t="shared" si="1"/>
+        <v>107</v>
+      </c>
+      <c r="D10" s="12">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E10" s="10">
+        <f t="shared" si="3"/>
+        <v>-9.7087378640776656E-3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <f>tsla!A11</f>
+        <v>45301</v>
+      </c>
+      <c r="B11" s="2">
+        <f>tsla!B11</f>
+        <v>108</v>
+      </c>
+      <c r="C11" s="2">
+        <f t="shared" si="1"/>
+        <v>108</v>
+      </c>
+      <c r="D11" s="12">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E11" s="10">
+        <f t="shared" si="3"/>
+        <v>-9.4339622641509413E-3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
+        <f>tsla!A12</f>
+        <v>45302</v>
+      </c>
+      <c r="B12" s="2">
+        <f>tsla!B12</f>
+        <v>110</v>
+      </c>
+      <c r="C12" s="2">
+        <f t="shared" si="1"/>
+        <v>110</v>
+      </c>
+      <c r="D12" s="12">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E12" s="10">
+        <f t="shared" si="3"/>
+        <v>-9.4339622641509413E-3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
+        <f>tsla!A13</f>
+        <v>45303</v>
+      </c>
+      <c r="B13" s="2">
+        <f>tsla!B13</f>
+        <v>109</v>
+      </c>
+      <c r="C13" s="2">
+        <f t="shared" si="1"/>
+        <v>110</v>
+      </c>
+      <c r="D13" s="12">
+        <f t="shared" si="2"/>
+        <v>-9.0909090909090384E-3</v>
+      </c>
+      <c r="E13" s="10">
+        <f t="shared" si="3"/>
+        <v>-9.4339622641509413E-3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
+        <f>tsla!A14</f>
+        <v>45304</v>
+      </c>
+      <c r="B14" s="2">
+        <f>tsla!B14</f>
+        <v>111</v>
+      </c>
+      <c r="C14" s="2">
+        <f t="shared" si="1"/>
+        <v>111</v>
+      </c>
+      <c r="D14" s="12">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E14" s="10">
+        <f t="shared" si="3"/>
+        <v>-9.0909090909090384E-3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
+        <f>tsla!A15</f>
+        <v>45305</v>
+      </c>
+      <c r="B15" s="2">
+        <f>tsla!B15</f>
+        <v>112</v>
+      </c>
+      <c r="C15" s="2">
+        <f t="shared" si="1"/>
+        <v>112</v>
+      </c>
+      <c r="D15" s="12">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E15" s="10">
+        <f t="shared" si="3"/>
+        <v>-9.0909090909090384E-3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
+        <f>tsla!A16</f>
+        <v>45306</v>
+      </c>
+      <c r="B16" s="2">
+        <f>tsla!B16</f>
+        <v>113</v>
+      </c>
+      <c r="C16" s="2">
+        <f t="shared" si="1"/>
+        <v>113</v>
+      </c>
+      <c r="D16" s="12">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="E16" s="10">
+        <f t="shared" si="3"/>
+        <v>-9.0909090909090384E-3</v>
+      </c>
+    </row>
+    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B17" s="2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5489E0B3-9DFD-4428-97EC-7729CAA254FB}">
+  <dimension ref="A1:I17"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="12.42578125" customWidth="1"/>
+    <col min="6" max="6" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="11" customWidth="1"/>
+    <col min="9" max="9" width="12.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B1" s="2" t="str">
+        <f>tsla!B1</f>
+        <v>close</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="F1" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="G1" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
+        <f>tsla!A2</f>
+        <v>45292</v>
+      </c>
+      <c r="B2" s="2">
+        <f>tsla!B2</f>
+        <v>100</v>
+      </c>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2">
+        <f>B2</f>
+        <v>100</v>
+      </c>
+      <c r="F2" s="12">
+        <f>B2/E2 - 1</f>
+        <v>0</v>
+      </c>
+      <c r="G2" s="10">
+        <f>F2</f>
+        <v>0</v>
+      </c>
+      <c r="H2" s="10">
+        <f>ABS(G2)</f>
+        <v>0</v>
+      </c>
+      <c r="I2" s="10"/>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <f>tsla!A3</f>
+        <v>45293</v>
+      </c>
+      <c r="B3" s="2">
+        <f>tsla!B3</f>
+        <v>102</v>
+      </c>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2">
+        <f>MAX(B2:B3)</f>
+        <v>102</v>
+      </c>
+      <c r="F3" s="12">
+        <f>B3/E3 - 1</f>
+        <v>0</v>
+      </c>
+      <c r="G3" s="10">
+        <f>MIN(F2:F3)</f>
+        <v>0</v>
+      </c>
+      <c r="H3" s="10">
+        <f t="shared" ref="H3:H16" si="0">ABS(G3)</f>
+        <v>0</v>
+      </c>
+      <c r="I3" s="10"/>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <f>tsla!A4</f>
+        <v>45294</v>
+      </c>
+      <c r="B4" s="2">
+        <f>tsla!B4</f>
+        <v>101</v>
+      </c>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2">
+        <f>MAX(B2:B4)</f>
+        <v>102</v>
+      </c>
+      <c r="F4" s="12">
+        <f>B4/E4 - 1</f>
+        <v>-9.8039215686274161E-3</v>
+      </c>
+      <c r="G4" s="10">
+        <f>MIN(F2:F4)</f>
+        <v>-9.8039215686274161E-3</v>
+      </c>
+      <c r="H4" s="10">
+        <f t="shared" si="0"/>
+        <v>9.8039215686274161E-3</v>
+      </c>
+      <c r="I4" s="10"/>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <f>tsla!A5</f>
+        <v>45295</v>
+      </c>
+      <c r="B5" s="2">
+        <f>tsla!B5</f>
+        <v>103</v>
+      </c>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2">
+        <f>MAX(B2:B5)</f>
+        <v>103</v>
+      </c>
+      <c r="F5" s="12">
+        <f>B5/E5 - 1</f>
+        <v>0</v>
+      </c>
+      <c r="G5" s="10">
+        <f>MIN(F2:F5)</f>
+        <v>-9.8039215686274161E-3</v>
+      </c>
+      <c r="H5" s="10">
+        <f t="shared" si="0"/>
+        <v>9.8039215686274161E-3</v>
+      </c>
+      <c r="I5" s="10"/>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <f>tsla!A6</f>
+        <v>45296</v>
+      </c>
+      <c r="B6" s="2">
+        <f>tsla!B6</f>
+        <v>102</v>
+      </c>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2">
+        <f>MAX(B2:B6)</f>
+        <v>103</v>
+      </c>
+      <c r="F6" s="12">
+        <f>B6/E6 - 1</f>
+        <v>-9.7087378640776656E-3</v>
+      </c>
+      <c r="G6" s="10">
+        <f>MIN(F2:F6)</f>
+        <v>-9.8039215686274161E-3</v>
+      </c>
+      <c r="H6" s="10">
+        <f t="shared" si="0"/>
+        <v>9.8039215686274161E-3</v>
+      </c>
+      <c r="I6" s="10"/>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <f>tsla!A7</f>
+        <v>45297</v>
+      </c>
+      <c r="B7" s="2">
+        <f>tsla!B7</f>
+        <v>104</v>
+      </c>
+      <c r="C7" s="2">
+        <f>B2</f>
+        <v>100</v>
+      </c>
+      <c r="D7" s="2">
+        <f>(B7/C7)^(252/5) - 1</f>
+        <v>6.2190541699069932</v>
+      </c>
+      <c r="E7" s="2">
+        <f>MAX(B3:B7)</f>
+        <v>104</v>
+      </c>
+      <c r="F7" s="12">
+        <f>B7/E7 - 1</f>
+        <v>0</v>
+      </c>
+      <c r="G7" s="10">
+        <f t="shared" ref="G7:G16" si="1">MIN(F3:F7)</f>
+        <v>-9.8039215686274161E-3</v>
+      </c>
+      <c r="H7" s="10">
+        <f t="shared" si="0"/>
+        <v>9.8039215686274161E-3</v>
+      </c>
+      <c r="I7" s="10">
+        <f>D7/H7</f>
+        <v>634.3435253305156</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <f>tsla!A8</f>
+        <v>45298</v>
+      </c>
+      <c r="B8" s="2">
+        <f>tsla!B8</f>
+        <v>106</v>
+      </c>
+      <c r="C8" s="2">
+        <f t="shared" ref="C8:C16" si="2">B3</f>
+        <v>102</v>
+      </c>
+      <c r="D8" s="2">
+        <f t="shared" ref="D8:D16" si="3">(B8/C8)^(252/5) - 1</f>
+        <v>5.9497143201739604</v>
+      </c>
+      <c r="E8" s="2">
+        <f>MAX(B4:B8)</f>
+        <v>106</v>
+      </c>
+      <c r="F8" s="12">
+        <f>B8/E8 - 1</f>
+        <v>0</v>
+      </c>
+      <c r="G8" s="10">
+        <f t="shared" si="1"/>
+        <v>-9.8039215686274161E-3</v>
+      </c>
+      <c r="H8" s="10">
+        <f t="shared" si="0"/>
+        <v>9.8039215686274161E-3</v>
+      </c>
+      <c r="I8" s="10">
+        <f t="shared" ref="I8:I16" si="4">D8/H8</f>
+        <v>606.87086065774611</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <f>tsla!A9</f>
+        <v>45299</v>
+      </c>
+      <c r="B9" s="2">
+        <f>tsla!B9</f>
+        <v>105</v>
+      </c>
+      <c r="C9" s="2">
+        <f t="shared" si="2"/>
+        <v>101</v>
+      </c>
+      <c r="D9" s="2">
+        <f t="shared" si="3"/>
+        <v>6.0817963632045959</v>
+      </c>
+      <c r="E9" s="2">
+        <f>MAX(B5:B9)</f>
+        <v>106</v>
+      </c>
+      <c r="F9" s="12">
+        <f>B9/E9 - 1</f>
+        <v>-9.4339622641509413E-3</v>
+      </c>
+      <c r="G9" s="10">
+        <f t="shared" si="1"/>
+        <v>-9.7087378640776656E-3</v>
+      </c>
+      <c r="H9" s="10">
+        <f t="shared" si="0"/>
+        <v>9.7087378640776656E-3</v>
+      </c>
+      <c r="I9" s="10">
+        <f t="shared" si="4"/>
+        <v>626.42502541007366</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <f>tsla!A10</f>
+        <v>45300</v>
+      </c>
+      <c r="B10" s="2">
+        <f>tsla!B10</f>
+        <v>107</v>
+      </c>
+      <c r="C10" s="2">
+        <f t="shared" si="2"/>
+        <v>103</v>
+      </c>
+      <c r="D10" s="2">
+        <f t="shared" si="3"/>
+        <v>5.8225428215970529</v>
+      </c>
+      <c r="E10" s="2">
+        <f>MAX(B6:B10)</f>
+        <v>107</v>
+      </c>
+      <c r="F10" s="12">
+        <f>B10/E10 - 1</f>
+        <v>0</v>
+      </c>
+      <c r="G10" s="10">
+        <f t="shared" si="1"/>
+        <v>-9.7087378640776656E-3</v>
+      </c>
+      <c r="H10" s="10">
+        <f t="shared" si="0"/>
+        <v>9.7087378640776656E-3</v>
+      </c>
+      <c r="I10" s="10">
+        <f t="shared" si="4"/>
+        <v>599.72191062449667</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <f>tsla!A11</f>
+        <v>45301</v>
+      </c>
+      <c r="B11" s="2">
+        <f>tsla!B11</f>
+        <v>108</v>
+      </c>
+      <c r="C11" s="2">
+        <f t="shared" si="2"/>
+        <v>102</v>
+      </c>
+      <c r="D11" s="2">
+        <f t="shared" si="3"/>
+        <v>16.82824607176077</v>
+      </c>
+      <c r="E11" s="2">
+        <f>MAX(B7:B11)</f>
+        <v>108</v>
+      </c>
+      <c r="F11" s="12">
+        <f>B11/E11 - 1</f>
+        <v>0</v>
+      </c>
+      <c r="G11" s="10">
+        <f t="shared" si="1"/>
+        <v>-9.4339622641509413E-3</v>
+      </c>
+      <c r="H11" s="10">
+        <f t="shared" si="0"/>
+        <v>9.4339622641509413E-3</v>
+      </c>
+      <c r="I11" s="10">
+        <f t="shared" si="4"/>
+        <v>1783.7940836066421</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
+        <f>tsla!A12</f>
+        <v>45302</v>
+      </c>
+      <c r="B12" s="2">
+        <f>tsla!B12</f>
+        <v>110</v>
+      </c>
+      <c r="C12" s="2">
+        <f t="shared" si="2"/>
+        <v>104</v>
+      </c>
+      <c r="D12" s="2">
+        <f t="shared" si="3"/>
+        <v>15.893165286515586</v>
+      </c>
+      <c r="E12" s="2">
+        <f>MAX(B8:B12)</f>
+        <v>110</v>
+      </c>
+      <c r="F12" s="12">
+        <f>B12/E12 - 1</f>
+        <v>0</v>
+      </c>
+      <c r="G12" s="10">
+        <f t="shared" si="1"/>
+        <v>-9.4339622641509413E-3</v>
+      </c>
+      <c r="H12" s="10">
+        <f t="shared" si="0"/>
+        <v>9.4339622641509413E-3</v>
+      </c>
+      <c r="I12" s="10">
+        <f t="shared" si="4"/>
+        <v>1684.6755203706525</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
+        <f>tsla!A13</f>
+        <v>45303</v>
+      </c>
+      <c r="B13" s="2">
+        <f>tsla!B13</f>
+        <v>109</v>
+      </c>
+      <c r="C13" s="2">
+        <f t="shared" si="2"/>
+        <v>106</v>
+      </c>
+      <c r="D13" s="2">
+        <f t="shared" si="3"/>
+        <v>3.0820647276156903</v>
+      </c>
+      <c r="E13" s="2">
+        <f>MAX(B9:B13)</f>
+        <v>110</v>
+      </c>
+      <c r="F13" s="12">
+        <f>B13/E13 - 1</f>
+        <v>-9.0909090909090384E-3</v>
+      </c>
+      <c r="G13" s="10">
+        <f t="shared" si="1"/>
+        <v>-9.4339622641509413E-3</v>
+      </c>
+      <c r="H13" s="10">
+        <f t="shared" si="0"/>
+        <v>9.4339622641509413E-3</v>
+      </c>
+      <c r="I13" s="10">
+        <f t="shared" si="4"/>
+        <v>326.69886112726323</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
+        <f>tsla!A14</f>
+        <v>45304</v>
+      </c>
+      <c r="B14" s="2">
+        <f>tsla!B14</f>
+        <v>111</v>
+      </c>
+      <c r="C14" s="2">
+        <f t="shared" si="2"/>
+        <v>105</v>
+      </c>
+      <c r="D14" s="2">
+        <f t="shared" si="3"/>
+        <v>15.456499378914341</v>
+      </c>
+      <c r="E14" s="2">
+        <f>MAX(B10:B14)</f>
+        <v>111</v>
+      </c>
+      <c r="F14" s="12">
+        <f>B14/E14 - 1</f>
+        <v>0</v>
+      </c>
+      <c r="G14" s="10">
+        <f t="shared" si="1"/>
+        <v>-9.0909090909090384E-3</v>
+      </c>
+      <c r="H14" s="10">
+        <f t="shared" si="0"/>
+        <v>9.0909090909090384E-3</v>
+      </c>
+      <c r="I14" s="10">
+        <f t="shared" si="4"/>
+        <v>1700.2149316805874</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
+        <f>tsla!A15</f>
+        <v>45305</v>
+      </c>
+      <c r="B15" s="2">
+        <f>tsla!B15</f>
+        <v>112</v>
+      </c>
+      <c r="C15" s="2">
+        <f t="shared" si="2"/>
+        <v>107</v>
+      </c>
+      <c r="D15" s="2">
+        <f t="shared" si="3"/>
+        <v>8.9918509561371689</v>
+      </c>
+      <c r="E15" s="2">
+        <f>MAX(B11:B15)</f>
+        <v>112</v>
+      </c>
+      <c r="F15" s="12">
+        <f>B15/E15 - 1</f>
+        <v>0</v>
+      </c>
+      <c r="G15" s="10">
+        <f t="shared" si="1"/>
+        <v>-9.0909090909090384E-3</v>
+      </c>
+      <c r="H15" s="10">
+        <f t="shared" si="0"/>
+        <v>9.0909090909090384E-3</v>
+      </c>
+      <c r="I15" s="10">
+        <f t="shared" si="4"/>
+        <v>989.10360517509434</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
+        <f>tsla!A16</f>
+        <v>45306</v>
+      </c>
+      <c r="B16" s="2">
+        <f>tsla!B16</f>
+        <v>113</v>
+      </c>
+      <c r="C16" s="2">
+        <f t="shared" si="2"/>
+        <v>108</v>
+      </c>
+      <c r="D16" s="2">
+        <f t="shared" si="3"/>
+        <v>8.7857986372559935</v>
+      </c>
+      <c r="E16" s="2">
+        <f>MAX(B12:B16)</f>
+        <v>113</v>
+      </c>
+      <c r="F16" s="12">
+        <f>B16/E16 - 1</f>
+        <v>0</v>
+      </c>
+      <c r="G16" s="10">
+        <f t="shared" si="1"/>
+        <v>-9.0909090909090384E-3</v>
+      </c>
+      <c r="H16" s="10">
+        <f t="shared" si="0"/>
+        <v>9.0909090909090384E-3</v>
+      </c>
+      <c r="I16" s="10">
+        <f t="shared" si="4"/>
+        <v>966.43785009816486</v>
+      </c>
+    </row>
+    <row r="17" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B17" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
+      <c r="E17" s="2"/>
+      <c r="F17" s="12"/>
+      <c r="G17" s="10"/>
+      <c r="H17" s="10"/>
+      <c r="I17" s="10"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A3B81E0-C2D8-4CAA-9B15-B00E1F7B2D2A}">
+  <dimension ref="A1:M19"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="13.7109375" customWidth="1"/>
+    <col min="3" max="4" width="9.140625" style="2"/>
+    <col min="5" max="5" width="18.42578125" style="10" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.85546875" style="10" customWidth="1"/>
+    <col min="7" max="10" width="13.140625" style="10" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.42578125" customWidth="1"/>
+    <col min="12" max="13" width="11.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="B1" s="2" t="str">
+        <f>tsla!B1</f>
+        <v>close</v>
+      </c>
+      <c r="C1" s="2" t="str">
+        <f>'sp500'!B1</f>
+        <v>close</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>114</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="G1" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="J1" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="K1" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="L1" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="M1" s="13" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
+        <f>tsla!A2</f>
+        <v>45292</v>
+      </c>
+      <c r="B2" s="2">
+        <f>tsla!B2</f>
+        <v>100</v>
+      </c>
+      <c r="C2" s="2">
+        <f>'sp500'!B2</f>
+        <v>100</v>
+      </c>
+      <c r="D2" s="2">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <f>tsla!A3</f>
+        <v>45293</v>
+      </c>
+      <c r="B3" s="2">
+        <f>tsla!B3</f>
+        <v>102</v>
+      </c>
+      <c r="C3" s="2">
+        <f>'sp500'!B3</f>
+        <v>101</v>
+      </c>
+      <c r="D3" s="2">
+        <f>D2</f>
+        <v>0.01</v>
+      </c>
+      <c r="E3" s="10">
+        <f>(C3-C2)/C2</f>
+        <v>0.01</v>
+      </c>
+      <c r="F3" s="10">
+        <f>(B3-B2)/B2</f>
+        <v>0.02</v>
+      </c>
+      <c r="G3" s="10">
+        <f>((1+D3)^(1/252))-1</f>
+        <v>3.9486219453710447E-5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <f>tsla!A4</f>
+        <v>45294</v>
+      </c>
+      <c r="B4" s="2">
+        <f>tsla!B4</f>
+        <v>101</v>
+      </c>
+      <c r="C4" s="2">
+        <f>'sp500'!B4</f>
+        <v>102</v>
+      </c>
+      <c r="D4" s="2">
+        <f t="shared" ref="D4:D16" si="0">D3</f>
+        <v>0.01</v>
+      </c>
+      <c r="E4" s="10">
+        <f t="shared" ref="E4:E16" si="1">(C4-C3)/C3</f>
+        <v>9.9009900990099011E-3</v>
+      </c>
+      <c r="F4" s="10">
+        <f t="shared" ref="F4:F16" si="2">(B4-B3)/B3</f>
+        <v>-9.8039215686274508E-3</v>
+      </c>
+      <c r="G4" s="10">
+        <f t="shared" ref="G4:G16" si="3">((1+D4)^(1/252))-1</f>
+        <v>3.9486219453710447E-5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <f>tsla!A5</f>
+        <v>45295</v>
+      </c>
+      <c r="B5" s="2">
+        <f>tsla!B5</f>
+        <v>103</v>
+      </c>
+      <c r="C5" s="2">
+        <f>'sp500'!B5</f>
+        <v>101</v>
+      </c>
+      <c r="D5" s="2">
+        <f t="shared" si="0"/>
+        <v>0.01</v>
+      </c>
+      <c r="E5" s="10">
+        <f t="shared" si="1"/>
+        <v>-9.8039215686274508E-3</v>
+      </c>
+      <c r="F5" s="10">
+        <f t="shared" si="2"/>
+        <v>1.9801980198019802E-2</v>
+      </c>
+      <c r="G5" s="10">
+        <f t="shared" si="3"/>
+        <v>3.9486219453710447E-5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <f>tsla!A6</f>
+        <v>45296</v>
+      </c>
+      <c r="B6" s="2">
+        <f>tsla!B6</f>
+        <v>102</v>
+      </c>
+      <c r="C6" s="2">
+        <f>'sp500'!B6</f>
+        <v>102</v>
+      </c>
+      <c r="D6" s="2">
+        <f t="shared" si="0"/>
+        <v>0.01</v>
+      </c>
+      <c r="E6" s="10">
+        <f t="shared" si="1"/>
+        <v>9.9009900990099011E-3</v>
+      </c>
+      <c r="F6" s="10">
+        <f t="shared" si="2"/>
+        <v>-9.7087378640776691E-3</v>
+      </c>
+      <c r="G6" s="10">
+        <f t="shared" si="3"/>
+        <v>3.9486219453710447E-5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <f>tsla!A7</f>
+        <v>45297</v>
+      </c>
+      <c r="B7" s="2">
+        <f>tsla!B7</f>
+        <v>104</v>
+      </c>
+      <c r="C7" s="2">
+        <f>'sp500'!B7</f>
+        <v>103</v>
+      </c>
+      <c r="D7" s="2">
+        <f t="shared" si="0"/>
+        <v>0.01</v>
+      </c>
+      <c r="E7" s="10">
+        <f t="shared" si="1"/>
+        <v>9.8039215686274508E-3</v>
+      </c>
+      <c r="F7" s="10">
+        <f t="shared" si="2"/>
+        <v>1.9607843137254902E-2</v>
+      </c>
+      <c r="G7" s="10">
+        <f t="shared" si="3"/>
+        <v>3.9486219453710447E-5</v>
+      </c>
+      <c r="H7" s="10">
+        <f>SLOPE(F3:F7,E3:E7)</f>
+        <v>-0.74969365048919212</v>
+      </c>
+      <c r="I7" s="10">
+        <f>AVERAGE(F3:F7)</f>
+        <v>7.9794327805139172E-3</v>
+      </c>
+      <c r="J7" s="10">
+        <f>AVERAGE(E3:E7)</f>
+        <v>5.9603960396039605E-3</v>
+      </c>
+      <c r="K7" s="12">
+        <f>AVERAGE(G3:G7)</f>
+        <v>3.9486219453710447E-5</v>
+      </c>
+      <c r="L7" s="12">
+        <f>K7+H7*(J7-K7)</f>
+        <v>-4.3993822778320363E-3</v>
+      </c>
+      <c r="M7" s="12">
+        <f>I7-L7</f>
+        <v>1.2378815058345954E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <f>tsla!A8</f>
+        <v>45298</v>
+      </c>
+      <c r="B8" s="2">
+        <f>tsla!B8</f>
+        <v>106</v>
+      </c>
+      <c r="C8" s="2">
+        <f>'sp500'!B8</f>
+        <v>104</v>
+      </c>
+      <c r="D8" s="2">
+        <f t="shared" si="0"/>
+        <v>0.01</v>
+      </c>
+      <c r="E8" s="10">
+        <f t="shared" si="1"/>
+        <v>9.7087378640776691E-3</v>
+      </c>
+      <c r="F8" s="10">
+        <f t="shared" si="2"/>
+        <v>1.9230769230769232E-2</v>
+      </c>
+      <c r="G8" s="10">
+        <f t="shared" si="3"/>
+        <v>3.9486219453710447E-5</v>
+      </c>
+      <c r="H8" s="10">
+        <f t="shared" ref="H8:H16" si="4">SLOPE(F4:F8,E4:E8)</f>
+        <v>-0.77609829655652762</v>
+      </c>
+      <c r="I8" s="10">
+        <f t="shared" ref="I8:I16" si="5">AVERAGE(F4:F8)</f>
+        <v>7.8255866266677635E-3</v>
+      </c>
+      <c r="J8" s="10">
+        <f t="shared" ref="J8:J16" si="6">AVERAGE(E4:E8)</f>
+        <v>5.9021436124194939E-3</v>
+      </c>
+      <c r="K8" s="12">
+        <f t="shared" ref="K8:K16" si="7">AVERAGE(G4:G8)</f>
+        <v>3.9486219453710447E-5</v>
+      </c>
+      <c r="L8" s="12">
+        <f t="shared" ref="L8:L16" si="8">K8+H8*(J8-K8)</f>
+        <v>-4.5105121965215676E-3</v>
+      </c>
+      <c r="M8" s="12">
+        <f t="shared" ref="M8:M16" si="9">I8-L8</f>
+        <v>1.2336098823189331E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <f>tsla!A9</f>
+        <v>45299</v>
+      </c>
+      <c r="B9" s="2">
+        <f>tsla!B9</f>
+        <v>105</v>
+      </c>
+      <c r="C9" s="2">
+        <f>'sp500'!B9</f>
+        <v>103</v>
+      </c>
+      <c r="D9" s="2">
+        <f t="shared" si="0"/>
+        <v>0.01</v>
+      </c>
+      <c r="E9" s="10">
+        <f t="shared" si="1"/>
+        <v>-9.6153846153846159E-3</v>
+      </c>
+      <c r="F9" s="10">
+        <f t="shared" si="2"/>
+        <v>-9.433962264150943E-3</v>
+      </c>
+      <c r="G9" s="10">
+        <f t="shared" si="3"/>
+        <v>3.9486219453710447E-5</v>
+      </c>
+      <c r="H9" s="10">
+        <f t="shared" si="4"/>
+        <v>0.21977437415125722</v>
+      </c>
+      <c r="I9" s="10">
+        <f t="shared" si="5"/>
+        <v>7.8995784875630654E-3</v>
+      </c>
+      <c r="J9" s="10">
+        <f t="shared" si="6"/>
+        <v>1.9988686695405905E-3</v>
+      </c>
+      <c r="K9" s="12">
+        <f t="shared" si="7"/>
+        <v>3.9486219453710447E-5</v>
+      </c>
+      <c r="L9" s="12">
+        <f t="shared" si="8"/>
+        <v>4.7010827114451153E-4</v>
+      </c>
+      <c r="M9" s="12">
+        <f t="shared" si="9"/>
+        <v>7.4294702164185537E-3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <f>tsla!A10</f>
+        <v>45300</v>
+      </c>
+      <c r="B10" s="2">
+        <f>tsla!B10</f>
+        <v>107</v>
+      </c>
+      <c r="C10" s="2">
+        <f>'sp500'!B10</f>
+        <v>104</v>
+      </c>
+      <c r="D10" s="2">
+        <f t="shared" si="0"/>
+        <v>0.01</v>
+      </c>
+      <c r="E10" s="10">
+        <f t="shared" si="1"/>
+        <v>9.7087378640776691E-3</v>
+      </c>
+      <c r="F10" s="10">
+        <f t="shared" si="2"/>
+        <v>1.9047619047619049E-2</v>
+      </c>
+      <c r="G10" s="10">
+        <f t="shared" si="3"/>
+        <v>3.9486219453710447E-5</v>
+      </c>
+      <c r="H10" s="10">
+        <f t="shared" si="4"/>
+        <v>1.0957641160462135</v>
+      </c>
+      <c r="I10" s="10">
+        <f t="shared" si="5"/>
+        <v>7.7487062574829136E-3</v>
+      </c>
+      <c r="J10" s="10">
+        <f t="shared" si="6"/>
+        <v>5.901400556081615E-3</v>
+      </c>
+      <c r="K10" s="12">
+        <f t="shared" si="7"/>
+        <v>3.9486219453710447E-5</v>
+      </c>
+      <c r="L10" s="12">
+        <f t="shared" si="8"/>
+        <v>6.4627616008674123E-3</v>
+      </c>
+      <c r="M10" s="12">
+        <f t="shared" si="9"/>
+        <v>1.2859446566155014E-3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <f>tsla!A11</f>
+        <v>45301</v>
+      </c>
+      <c r="B11" s="2">
+        <f>tsla!B11</f>
+        <v>108</v>
+      </c>
+      <c r="C11" s="2">
+        <f>'sp500'!B11</f>
+        <v>104</v>
+      </c>
+      <c r="D11" s="2">
+        <f t="shared" si="0"/>
+        <v>0.01</v>
+      </c>
+      <c r="E11" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F11" s="10">
+        <f t="shared" si="2"/>
+        <v>9.3457943925233638E-3</v>
+      </c>
+      <c r="G11" s="10">
+        <f t="shared" si="3"/>
+        <v>3.9486219453710447E-5</v>
+      </c>
+      <c r="H11" s="10">
+        <f t="shared" si="4"/>
+        <v>1.4254629865087485</v>
+      </c>
+      <c r="I11" s="10">
+        <f t="shared" si="5"/>
+        <v>1.1559612708803121E-2</v>
+      </c>
+      <c r="J11" s="10">
+        <f t="shared" si="6"/>
+        <v>3.9212025362796348E-3</v>
+      </c>
+      <c r="K11" s="12">
+        <f t="shared" si="7"/>
+        <v>3.9486219453710447E-5</v>
+      </c>
+      <c r="L11" s="12">
+        <f t="shared" si="8"/>
+        <v>5.5727291532161318E-3</v>
+      </c>
+      <c r="M11" s="12">
+        <f t="shared" si="9"/>
+        <v>5.9868835555869889E-3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
+        <f>tsla!A12</f>
+        <v>45302</v>
+      </c>
+      <c r="B12" s="2">
+        <f>tsla!B12</f>
+        <v>110</v>
+      </c>
+      <c r="C12" s="2">
+        <f>'sp500'!B12</f>
+        <v>105</v>
+      </c>
+      <c r="D12" s="2">
+        <f t="shared" si="0"/>
+        <v>0.01</v>
+      </c>
+      <c r="E12" s="10">
+        <f t="shared" si="1"/>
+        <v>9.6153846153846159E-3</v>
+      </c>
+      <c r="F12" s="10">
+        <f t="shared" si="2"/>
+        <v>1.8518518518518517E-2</v>
+      </c>
+      <c r="G12" s="10">
+        <f t="shared" si="3"/>
+        <v>3.9486219453710447E-5</v>
+      </c>
+      <c r="H12" s="10">
+        <f t="shared" si="4"/>
+        <v>1.4098943003724727</v>
+      </c>
+      <c r="I12" s="10">
+        <f t="shared" si="5"/>
+        <v>1.1341747785055844E-2</v>
+      </c>
+      <c r="J12" s="10">
+        <f t="shared" si="6"/>
+        <v>3.8834951456310678E-3</v>
+      </c>
+      <c r="K12" s="12">
+        <f t="shared" si="7"/>
+        <v>3.9486219453710447E-5</v>
+      </c>
+      <c r="L12" s="12">
+        <f t="shared" si="8"/>
+        <v>5.4591324950520759E-3</v>
+      </c>
+      <c r="M12" s="12">
+        <f t="shared" si="9"/>
+        <v>5.8826152900037683E-3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
+        <f>tsla!A13</f>
+        <v>45303</v>
+      </c>
+      <c r="B13" s="2">
+        <f>tsla!B13</f>
+        <v>109</v>
+      </c>
+      <c r="C13" s="2">
+        <f>'sp500'!B13</f>
+        <v>105</v>
+      </c>
+      <c r="D13" s="2">
+        <f t="shared" si="0"/>
+        <v>0.01</v>
+      </c>
+      <c r="E13" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F13" s="10">
+        <f t="shared" si="2"/>
+        <v>-9.0909090909090905E-3</v>
+      </c>
+      <c r="G13" s="10">
+        <f t="shared" si="3"/>
+        <v>3.9486219453710447E-5</v>
+      </c>
+      <c r="H13" s="10">
+        <f t="shared" si="4"/>
+        <v>1.5311284138129952</v>
+      </c>
+      <c r="I13" s="10">
+        <f t="shared" si="5"/>
+        <v>5.6774121207201801E-3</v>
+      </c>
+      <c r="J13" s="10">
+        <f t="shared" si="6"/>
+        <v>1.9417475728155339E-3</v>
+      </c>
+      <c r="K13" s="12">
+        <f t="shared" si="7"/>
+        <v>3.9486219453710447E-5</v>
+      </c>
+      <c r="L13" s="12">
+        <f t="shared" si="8"/>
+        <v>2.9520926280843609E-3</v>
+      </c>
+      <c r="M13" s="12">
+        <f t="shared" si="9"/>
+        <v>2.7253194926358192E-3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
+        <f>tsla!A14</f>
+        <v>45304</v>
+      </c>
+      <c r="B14" s="2">
+        <f>tsla!B14</f>
+        <v>111</v>
+      </c>
+      <c r="C14" s="2">
+        <f>'sp500'!B14</f>
+        <v>106</v>
+      </c>
+      <c r="D14" s="2">
+        <f t="shared" si="0"/>
+        <v>0.01</v>
+      </c>
+      <c r="E14" s="10">
+        <f t="shared" si="1"/>
+        <v>9.5238095238095247E-3</v>
+      </c>
+      <c r="F14" s="10">
+        <f t="shared" si="2"/>
+        <v>1.834862385321101E-2</v>
+      </c>
+      <c r="G14" s="10">
+        <f t="shared" si="3"/>
+        <v>3.9486219453710447E-5</v>
+      </c>
+      <c r="H14" s="10">
+        <f t="shared" si="4"/>
+        <v>1.9252924339695721</v>
+      </c>
+      <c r="I14" s="10">
+        <f t="shared" si="5"/>
+        <v>1.123392934419257E-2</v>
+      </c>
+      <c r="J14" s="10">
+        <f t="shared" si="6"/>
+        <v>5.7695864006543623E-3</v>
+      </c>
+      <c r="K14" s="12">
+        <f t="shared" si="7"/>
+        <v>3.9486219453710447E-5</v>
+      </c>
+      <c r="L14" s="12">
+        <f t="shared" si="8"/>
+        <v>1.1071604744206999E-2</v>
+      </c>
+      <c r="M14" s="12">
+        <f t="shared" si="9"/>
+        <v>1.6232459998557179E-4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
+        <f>tsla!A15</f>
+        <v>45305</v>
+      </c>
+      <c r="B15" s="2">
+        <f>tsla!B15</f>
+        <v>112</v>
+      </c>
+      <c r="C15" s="2">
+        <f>'sp500'!B15</f>
+        <v>106</v>
+      </c>
+      <c r="D15" s="2">
+        <f t="shared" si="0"/>
+        <v>0.01</v>
+      </c>
+      <c r="E15" s="10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F15" s="10">
+        <f t="shared" si="2"/>
+        <v>9.0090090090090089E-3</v>
+      </c>
+      <c r="G15" s="10">
+        <f t="shared" si="3"/>
+        <v>3.9486219453710447E-5</v>
+      </c>
+      <c r="H15" s="10">
+        <f t="shared" si="4"/>
+        <v>1.6035887606882955</v>
+      </c>
+      <c r="I15" s="10">
+        <f t="shared" si="5"/>
+        <v>9.2262073364705616E-3</v>
+      </c>
+      <c r="J15" s="10">
+        <f t="shared" si="6"/>
+        <v>3.8278388278388279E-3</v>
+      </c>
+      <c r="K15" s="12">
+        <f t="shared" si="7"/>
+        <v>3.9486219453710447E-5</v>
+      </c>
+      <c r="L15" s="12">
+        <f t="shared" si="8"/>
+        <v>6.1144458837842728E-3</v>
+      </c>
+      <c r="M15" s="12">
+        <f t="shared" si="9"/>
+        <v>3.1117614526862888E-3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
+        <f>tsla!A16</f>
+        <v>45306</v>
+      </c>
+      <c r="B16" s="2">
+        <f>tsla!B16</f>
+        <v>113</v>
+      </c>
+      <c r="C16" s="2">
+        <f>'sp500'!B16</f>
+        <v>107</v>
+      </c>
+      <c r="D16" s="2">
+        <f t="shared" si="0"/>
+        <v>0.01</v>
+      </c>
+      <c r="E16" s="10">
+        <f t="shared" si="1"/>
+        <v>9.433962264150943E-3</v>
+      </c>
+      <c r="F16" s="10">
+        <f t="shared" si="2"/>
+        <v>8.9285714285714281E-3</v>
+      </c>
+      <c r="G16" s="10">
+        <f t="shared" si="3"/>
+        <v>3.9486219453710447E-5</v>
+      </c>
+      <c r="H16" s="10">
+        <f t="shared" si="4"/>
+        <v>1.6147753323006508</v>
+      </c>
+      <c r="I16" s="10">
+        <f t="shared" si="5"/>
+        <v>9.1427627436801752E-3</v>
+      </c>
+      <c r="J16" s="10">
+        <f t="shared" si="6"/>
+        <v>5.7146312806690162E-3</v>
+      </c>
+      <c r="K16" s="12">
+        <f t="shared" si="7"/>
+        <v>3.9486219453710447E-5</v>
+      </c>
+      <c r="L16" s="12">
+        <f t="shared" si="8"/>
+        <v>9.2035704715320524E-3</v>
+      </c>
+      <c r="M16" s="12">
+        <f t="shared" si="9"/>
+        <v>-6.0807727851877255E-5</v>
+      </c>
+    </row>
+    <row r="17" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B17" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="18" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="L18" t="s">
+        <v>121</v>
+      </c>
+      <c r="M18" s="12">
+        <f>AVERAGE(M7:M16)</f>
+        <v>5.1238425417615904E-3</v>
+      </c>
+    </row>
+    <row r="19" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="L19" t="s">
+        <v>122</v>
+      </c>
+      <c r="M19" s="12">
+        <f>MEDIAN(M7:M16)</f>
+        <v>4.4971883713450286E-3</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -9353,23 +12695,23 @@
         <v>-13</v>
       </c>
       <c r="M17" s="2">
-        <f>D16-D17</f>
+        <f t="shared" ref="M17:M31" si="21">D16-D17</f>
         <v>13</v>
       </c>
       <c r="N17" t="b">
-        <f t="shared" ref="N17:N31" si="21">L17&gt;M17</f>
+        <f t="shared" ref="N17:N31" si="22">L17&gt;M17</f>
         <v>0</v>
       </c>
       <c r="O17" t="b">
-        <f t="shared" ref="O17:O31" si="22">L17&gt;0</f>
+        <f t="shared" ref="O17:O31" si="23">L17&gt;0</f>
         <v>0</v>
       </c>
       <c r="P17" t="b">
-        <f t="shared" ref="P17:P31" si="23">AND(N17:O17)</f>
+        <f t="shared" ref="P17:P31" si="24">AND(N17:O17)</f>
         <v>0</v>
       </c>
       <c r="Q17" s="2">
-        <f t="shared" ref="Q17:Q31" si="24">IF(P17,L17,0)</f>
+        <f t="shared" ref="Q17:Q31" si="25">IF(P17,L17,0)</f>
         <v>0</v>
       </c>
       <c r="R17" s="2">
@@ -9377,27 +12719,27 @@
         <v>1.0714285714285714</v>
       </c>
       <c r="S17" s="2">
-        <f t="shared" ref="S17:S31" si="25">R17*14</f>
+        <f t="shared" ref="S17:S31" si="26">R17*14</f>
         <v>15</v>
       </c>
       <c r="U17" t="b">
-        <f t="shared" ref="U17:U31" si="26">M17 &gt; L17</f>
+        <f t="shared" ref="U17:U31" si="27">M17 &gt; L17</f>
         <v>1</v>
       </c>
       <c r="V17" t="b">
-        <f t="shared" ref="V17:V31" si="27">M17 &gt; 0</f>
+        <f t="shared" ref="V17:V31" si="28">M17 &gt; 0</f>
         <v>1</v>
       </c>
       <c r="W17" t="b">
-        <f t="shared" ref="W17:W31" si="28">AND(U17:V17)</f>
+        <f t="shared" ref="W17:W31" si="29">AND(U17:V17)</f>
         <v>1</v>
       </c>
       <c r="X17" s="2">
-        <f t="shared" ref="X17:X31" si="29">IF(W17,M17, 0)</f>
+        <f t="shared" ref="X17:X31" si="30">IF(W17,M17, 0)</f>
         <v>13</v>
       </c>
       <c r="Y17">
-        <f t="shared" ref="Y17:Y31" si="30">AVERAGE(X4:X17)</f>
+        <f t="shared" ref="Y17:Y31" si="31">AVERAGE(X4:X17)</f>
         <v>1.2142857142857142</v>
       </c>
       <c r="Z17" s="2">
@@ -9405,41 +12747,41 @@
         <v>17</v>
       </c>
       <c r="AB17" s="10">
-        <f t="shared" ref="AB17:AB31" si="31">100 * (R17 / I17)</f>
+        <f t="shared" ref="AB17:AB31" si="32">100 * (R17 / I17)</f>
         <v>32.608695652173914</v>
       </c>
       <c r="AC17" s="10">
-        <f t="shared" ref="AC17:AC31" si="32">100 * (Y17 / I17)</f>
+        <f t="shared" ref="AC17:AC31" si="33">100 * (Y17 / I17)</f>
         <v>36.95652173913043</v>
       </c>
       <c r="AD17" s="2">
-        <f t="shared" ref="AD17:AD31" si="33">AB17-AC17</f>
+        <f t="shared" ref="AD17:AD31" si="34">AB17-AC17</f>
         <v>-4.3478260869565162</v>
       </c>
       <c r="AE17" s="2">
-        <f t="shared" ref="AE17:AE31" si="34">AB17+AC17</f>
+        <f t="shared" ref="AE17:AE31" si="35">AB17+AC17</f>
         <v>69.565217391304344</v>
       </c>
       <c r="AF17" s="10">
-        <f t="shared" ref="AF17:AF31" si="35">100*ABS(AD17/AE17)</f>
+        <f t="shared" ref="AF17:AF31" si="36">100*ABS(AD17/AE17)</f>
         <v>6.249999999999992</v>
       </c>
     </row>
     <row r="18" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
-        <f t="shared" ref="A18:A31" si="36">A17+1</f>
+        <f t="shared" ref="A18:A31" si="37">A17+1</f>
         <v>45308</v>
       </c>
       <c r="B18" s="2">
-        <f t="shared" ref="B18:D30" si="37">B3</f>
+        <f t="shared" ref="B18:D30" si="38">B3</f>
         <v>102</v>
       </c>
       <c r="C18" s="2">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>103</v>
       </c>
       <c r="D18" s="2">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>101</v>
       </c>
       <c r="E18" s="2">
@@ -9459,7 +12801,7 @@
         <v>3</v>
       </c>
       <c r="I18" s="2">
-        <f t="shared" ref="I18:I30" si="38">AVERAGE(H5:H18)</f>
+        <f t="shared" ref="I18:I30" si="39">AVERAGE(H5:H18)</f>
         <v>3.3571428571428572</v>
       </c>
       <c r="J18" s="2">
@@ -9471,51 +12813,51 @@
         <v>2</v>
       </c>
       <c r="M18" s="8">
-        <f>D17-D18</f>
+        <f t="shared" si="21"/>
         <v>-2</v>
       </c>
       <c r="N18" t="b">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>1</v>
       </c>
       <c r="O18" t="b">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>1</v>
       </c>
       <c r="P18" t="b">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>1</v>
       </c>
       <c r="Q18" s="2">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>2</v>
       </c>
       <c r="R18" s="2">
-        <f t="shared" ref="R17:R31" si="39">AVERAGE(Q5:Q18)</f>
+        <f t="shared" ref="R18:R31" si="40">AVERAGE(Q5:Q18)</f>
         <v>1.2142857142857142</v>
       </c>
       <c r="S18" s="2">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>17</v>
       </c>
       <c r="U18" t="b">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="V18" t="b">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="W18" t="b">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="X18" s="2">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="Y18">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>1.1428571428571428</v>
       </c>
       <c r="Z18" s="2">
@@ -9523,41 +12865,41 @@
         <v>16</v>
       </c>
       <c r="AB18" s="10">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>36.170212765957444</v>
       </c>
       <c r="AC18" s="10">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>34.042553191489361</v>
       </c>
       <c r="AD18" s="2">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>2.1276595744680833</v>
       </c>
       <c r="AE18" s="2">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>70.212765957446805</v>
       </c>
       <c r="AF18" s="10">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>3.0303030303030281</v>
       </c>
     </row>
     <row r="19" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>45309</v>
       </c>
       <c r="B19" s="2">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>101</v>
       </c>
       <c r="C19" s="2">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>102</v>
       </c>
       <c r="D19" s="2">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>100</v>
       </c>
       <c r="E19" s="2">
@@ -9589,51 +12931,51 @@
         <v>-1</v>
       </c>
       <c r="M19" s="2">
-        <f>D18-D19</f>
+        <f t="shared" si="21"/>
         <v>1</v>
       </c>
       <c r="N19" t="b">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="O19" t="b">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="P19" t="b">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="Q19" s="2">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="R19" s="2">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>1.0714285714285714</v>
       </c>
       <c r="S19" s="2">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>15</v>
       </c>
       <c r="U19" t="b">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
       <c r="V19" t="b">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="W19" t="b">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="X19" s="2">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="Y19">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>1.2142857142857142</v>
       </c>
       <c r="Z19" s="2">
@@ -9641,41 +12983,41 @@
         <v>17</v>
       </c>
       <c r="AB19" s="10">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>32.608695652173914</v>
       </c>
       <c r="AC19" s="10">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>36.95652173913043</v>
       </c>
       <c r="AD19" s="2">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>-4.3478260869565162</v>
       </c>
       <c r="AE19" s="2">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>69.565217391304344</v>
       </c>
       <c r="AF19" s="10">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>6.249999999999992</v>
       </c>
     </row>
     <row r="20" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>45310</v>
       </c>
       <c r="B20" s="2">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>103</v>
       </c>
       <c r="C20" s="2">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>104</v>
       </c>
       <c r="D20" s="2">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>102</v>
       </c>
       <c r="E20" s="2">
@@ -9695,7 +13037,7 @@
         <v>3</v>
       </c>
       <c r="I20" s="2">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>3.3571428571428572</v>
       </c>
       <c r="J20" s="2">
@@ -9707,51 +13049,51 @@
         <v>2</v>
       </c>
       <c r="M20" s="2">
-        <f>D19-D20</f>
+        <f t="shared" si="21"/>
         <v>-2</v>
       </c>
       <c r="N20" t="b">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>1</v>
       </c>
       <c r="O20" t="b">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>1</v>
       </c>
       <c r="P20" t="b">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>1</v>
       </c>
       <c r="Q20" s="2">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>2</v>
       </c>
       <c r="R20" s="2">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>1.2142857142857142</v>
       </c>
       <c r="S20" s="2">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>17</v>
       </c>
       <c r="U20" t="b">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="V20" t="b">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="W20" t="b">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="X20" s="2">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="Y20">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>1.1428571428571428</v>
       </c>
       <c r="Z20" s="2">
@@ -9759,41 +13101,41 @@
         <v>16</v>
       </c>
       <c r="AB20" s="10">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>36.170212765957444</v>
       </c>
       <c r="AC20" s="10">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>34.042553191489361</v>
       </c>
       <c r="AD20" s="2">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>2.1276595744680833</v>
       </c>
       <c r="AE20" s="2">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>70.212765957446805</v>
       </c>
       <c r="AF20" s="10">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>3.0303030303030281</v>
       </c>
     </row>
     <row r="21" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>45311</v>
       </c>
       <c r="B21" s="2">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>102</v>
       </c>
       <c r="C21" s="2">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>103</v>
       </c>
       <c r="D21" s="2">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>101</v>
       </c>
       <c r="E21" s="2">
@@ -9813,7 +13155,7 @@
         <v>2</v>
       </c>
       <c r="I21" s="2">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>3.2857142857142856</v>
       </c>
       <c r="J21" s="2">
@@ -9825,51 +13167,51 @@
         <v>-1</v>
       </c>
       <c r="M21" s="2">
-        <f>D20-D21</f>
+        <f t="shared" si="21"/>
         <v>1</v>
       </c>
       <c r="N21" t="b">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="O21" t="b">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="P21" t="b">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="Q21" s="2">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="R21" s="2">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>1.0714285714285714</v>
       </c>
       <c r="S21" s="2">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>15</v>
       </c>
       <c r="U21" t="b">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
       <c r="V21" t="b">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="W21" t="b">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="X21" s="2">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="Y21">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>1.2142857142857142</v>
       </c>
       <c r="Z21" s="2">
@@ -9877,41 +13219,41 @@
         <v>17</v>
       </c>
       <c r="AB21" s="10">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>32.608695652173914</v>
       </c>
       <c r="AC21" s="10">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>36.95652173913043</v>
       </c>
       <c r="AD21" s="2">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>-4.3478260869565162</v>
       </c>
       <c r="AE21" s="2">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>69.565217391304344</v>
       </c>
       <c r="AF21" s="10">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>6.249999999999992</v>
       </c>
     </row>
     <row r="22" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>45312</v>
       </c>
       <c r="B22" s="2">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>104</v>
       </c>
       <c r="C22" s="2">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>105</v>
       </c>
       <c r="D22" s="2">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>103</v>
       </c>
       <c r="E22" s="2">
@@ -9943,51 +13285,51 @@
         <v>2</v>
       </c>
       <c r="M22" s="2">
-        <f>D21-D22</f>
+        <f t="shared" si="21"/>
         <v>-2</v>
       </c>
       <c r="N22" t="b">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>1</v>
       </c>
       <c r="O22" t="b">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>1</v>
       </c>
       <c r="P22" t="b">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>1</v>
       </c>
       <c r="Q22" s="2">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>2</v>
       </c>
       <c r="R22" s="2">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>1.0714285714285714</v>
       </c>
       <c r="S22" s="2">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>15</v>
       </c>
       <c r="U22" t="b">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="V22" t="b">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="W22" t="b">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="X22" s="2">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="Y22">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>1.2142857142857142</v>
       </c>
       <c r="Z22" s="2">
@@ -9995,41 +13337,41 @@
         <v>17</v>
       </c>
       <c r="AB22" s="10">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>32.608695652173914</v>
       </c>
       <c r="AC22" s="10">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>36.95652173913043</v>
       </c>
       <c r="AD22" s="2">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>-4.3478260869565162</v>
       </c>
       <c r="AE22" s="2">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>69.565217391304344</v>
       </c>
       <c r="AF22" s="10">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>6.249999999999992</v>
       </c>
     </row>
     <row r="23" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>45313</v>
       </c>
       <c r="B23" s="2">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>106</v>
       </c>
       <c r="C23" s="2">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>107</v>
       </c>
       <c r="D23" s="2">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>105</v>
       </c>
       <c r="E23" s="2">
@@ -10049,7 +13391,7 @@
         <v>3</v>
       </c>
       <c r="I23" s="2">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>3.3571428571428572</v>
       </c>
       <c r="J23" s="2">
@@ -10061,51 +13403,51 @@
         <v>2</v>
       </c>
       <c r="M23" s="2">
-        <f>D22-D23</f>
+        <f t="shared" si="21"/>
         <v>-2</v>
       </c>
       <c r="N23" t="b">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>1</v>
       </c>
       <c r="O23" t="b">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>1</v>
       </c>
       <c r="P23" t="b">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>1</v>
       </c>
       <c r="Q23" s="2">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>2</v>
       </c>
       <c r="R23" s="2">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>1.2142857142857142</v>
       </c>
       <c r="S23" s="2">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>17</v>
       </c>
       <c r="U23" t="b">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="V23" t="b">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="W23" t="b">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="X23" s="2">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="Y23">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>1.1428571428571428</v>
       </c>
       <c r="Z23" s="2">
@@ -10113,41 +13455,41 @@
         <v>16</v>
       </c>
       <c r="AB23" s="10">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>36.170212765957444</v>
       </c>
       <c r="AC23" s="10">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>34.042553191489361</v>
       </c>
       <c r="AD23" s="2">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>2.1276595744680833</v>
       </c>
       <c r="AE23" s="2">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>70.212765957446805</v>
       </c>
       <c r="AF23" s="10">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>3.0303030303030281</v>
       </c>
     </row>
     <row r="24" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>45314</v>
       </c>
       <c r="B24" s="2">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>105</v>
       </c>
       <c r="C24" s="2">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>106</v>
       </c>
       <c r="D24" s="2">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>104</v>
       </c>
       <c r="E24" s="2">
@@ -10167,7 +13509,7 @@
         <v>2</v>
       </c>
       <c r="I24" s="2">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>3.2857142857142856</v>
       </c>
       <c r="J24" s="2">
@@ -10179,51 +13521,51 @@
         <v>-1</v>
       </c>
       <c r="M24" s="2">
-        <f>D23-D24</f>
+        <f t="shared" si="21"/>
         <v>1</v>
       </c>
       <c r="N24" t="b">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="O24" t="b">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="P24" t="b">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="Q24" s="2">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="R24" s="2">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>1.0714285714285714</v>
       </c>
       <c r="S24" s="2">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>15</v>
       </c>
       <c r="U24" t="b">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
       <c r="V24" t="b">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="W24" t="b">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="X24" s="2">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="Y24">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>1.2142857142857142</v>
       </c>
       <c r="Z24" s="2">
@@ -10231,41 +13573,41 @@
         <v>17</v>
       </c>
       <c r="AB24" s="10">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>32.608695652173914</v>
       </c>
       <c r="AC24" s="10">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>36.95652173913043</v>
       </c>
       <c r="AD24" s="2">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>-4.3478260869565162</v>
       </c>
       <c r="AE24" s="2">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>69.565217391304344</v>
       </c>
       <c r="AF24" s="10">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>6.249999999999992</v>
       </c>
     </row>
     <row r="25" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>45315</v>
       </c>
       <c r="B25" s="2">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>107</v>
       </c>
       <c r="C25" s="2">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>108</v>
       </c>
       <c r="D25" s="2">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>106</v>
       </c>
       <c r="E25" s="2">
@@ -10285,7 +13627,7 @@
         <v>3</v>
       </c>
       <c r="I25" s="2">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>3.3571428571428572</v>
       </c>
       <c r="J25" s="2">
@@ -10297,51 +13639,51 @@
         <v>2</v>
       </c>
       <c r="M25" s="2">
-        <f>D24-D25</f>
+        <f t="shared" si="21"/>
         <v>-2</v>
       </c>
       <c r="N25" t="b">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>1</v>
       </c>
       <c r="O25" t="b">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>1</v>
       </c>
       <c r="P25" t="b">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>1</v>
       </c>
       <c r="Q25" s="2">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>2</v>
       </c>
       <c r="R25" s="2">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>1.1428571428571428</v>
       </c>
       <c r="S25" s="2">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>16</v>
       </c>
       <c r="U25" t="b">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="V25" t="b">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="W25" t="b">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="X25" s="2">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="Y25">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>1.2142857142857142</v>
       </c>
       <c r="Z25" s="2">
@@ -10349,41 +13691,41 @@
         <v>17</v>
       </c>
       <c r="AB25" s="10">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>34.042553191489361</v>
       </c>
       <c r="AC25" s="10">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>36.170212765957444</v>
       </c>
       <c r="AD25" s="2">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>-2.1276595744680833</v>
       </c>
       <c r="AE25" s="2">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>70.212765957446805</v>
       </c>
       <c r="AF25" s="10">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>3.0303030303030281</v>
       </c>
     </row>
     <row r="26" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>45316</v>
       </c>
       <c r="B26" s="2">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>108</v>
       </c>
       <c r="C26" s="2">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>109</v>
       </c>
       <c r="D26" s="2">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>107</v>
       </c>
       <c r="E26" s="2">
@@ -10403,7 +13745,7 @@
         <v>2</v>
       </c>
       <c r="I26" s="2">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>3.2857142857142856</v>
       </c>
       <c r="J26" s="2">
@@ -10415,51 +13757,51 @@
         <v>1</v>
       </c>
       <c r="M26" s="2">
-        <f>D25-D26</f>
+        <f t="shared" si="21"/>
         <v>-1</v>
       </c>
       <c r="N26" t="b">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>1</v>
       </c>
       <c r="O26" t="b">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>1</v>
       </c>
       <c r="P26" t="b">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>1</v>
       </c>
       <c r="Q26" s="2">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>1</v>
       </c>
       <c r="R26" s="2">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>1.0714285714285714</v>
       </c>
       <c r="S26" s="2">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>15</v>
       </c>
       <c r="U26" t="b">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="V26" t="b">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="W26" t="b">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="X26" s="2">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="Y26">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>1.2142857142857142</v>
       </c>
       <c r="Z26" s="2">
@@ -10467,41 +13809,41 @@
         <v>17</v>
       </c>
       <c r="AB26" s="10">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>32.608695652173914</v>
       </c>
       <c r="AC26" s="10">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>36.95652173913043</v>
       </c>
       <c r="AD26" s="2">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>-4.3478260869565162</v>
       </c>
       <c r="AE26" s="2">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>69.565217391304344</v>
       </c>
       <c r="AF26" s="10">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>6.249999999999992</v>
       </c>
     </row>
     <row r="27" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>45317</v>
       </c>
       <c r="B27" s="2">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>110</v>
       </c>
       <c r="C27" s="2">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>111</v>
       </c>
       <c r="D27" s="2">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>109</v>
       </c>
       <c r="E27" s="2">
@@ -10521,7 +13863,7 @@
         <v>3</v>
       </c>
       <c r="I27" s="2">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>3.3571428571428572</v>
       </c>
       <c r="J27" s="2">
@@ -10533,51 +13875,51 @@
         <v>2</v>
       </c>
       <c r="M27" s="2">
-        <f>D26-D27</f>
+        <f t="shared" si="21"/>
         <v>-2</v>
       </c>
       <c r="N27" t="b">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>1</v>
       </c>
       <c r="O27" t="b">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>1</v>
       </c>
       <c r="P27" t="b">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>1</v>
       </c>
       <c r="Q27" s="2">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>2</v>
       </c>
       <c r="R27" s="2">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>1.2142857142857142</v>
       </c>
       <c r="S27" s="2">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>17</v>
       </c>
       <c r="U27" t="b">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="V27" t="b">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="W27" t="b">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="X27" s="2">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="Y27">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>1.1428571428571428</v>
       </c>
       <c r="Z27" s="2">
@@ -10585,41 +13927,41 @@
         <v>16</v>
       </c>
       <c r="AB27" s="10">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>36.170212765957444</v>
       </c>
       <c r="AC27" s="10">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>34.042553191489361</v>
       </c>
       <c r="AD27" s="2">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>2.1276595744680833</v>
       </c>
       <c r="AE27" s="2">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>70.212765957446805</v>
       </c>
       <c r="AF27" s="10">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>3.0303030303030281</v>
       </c>
     </row>
     <row r="28" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>45318</v>
       </c>
       <c r="B28" s="2">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>109</v>
       </c>
       <c r="C28" s="2">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>110</v>
       </c>
       <c r="D28" s="2">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>108</v>
       </c>
       <c r="E28" s="2">
@@ -10639,7 +13981,7 @@
         <v>2</v>
       </c>
       <c r="I28" s="2">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>3.2857142857142856</v>
       </c>
       <c r="J28" s="2">
@@ -10651,51 +13993,51 @@
         <v>-1</v>
       </c>
       <c r="M28" s="2">
-        <f>D27-D28</f>
+        <f t="shared" si="21"/>
         <v>1</v>
       </c>
       <c r="N28" t="b">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="O28" t="b">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>0</v>
       </c>
       <c r="P28" t="b">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="Q28" s="2">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="R28" s="2">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>1.0714285714285714</v>
       </c>
       <c r="S28" s="2">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>15</v>
       </c>
       <c r="U28" t="b">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>1</v>
       </c>
       <c r="V28" t="b">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>1</v>
       </c>
       <c r="W28" t="b">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>1</v>
       </c>
       <c r="X28" s="2">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="Y28">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>1.2142857142857142</v>
       </c>
       <c r="Z28" s="2">
@@ -10703,41 +14045,41 @@
         <v>17</v>
       </c>
       <c r="AB28" s="10">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>32.608695652173914</v>
       </c>
       <c r="AC28" s="10">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>36.95652173913043</v>
       </c>
       <c r="AD28" s="2">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>-4.3478260869565162</v>
       </c>
       <c r="AE28" s="2">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>69.565217391304344</v>
       </c>
       <c r="AF28" s="10">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>6.249999999999992</v>
       </c>
     </row>
     <row r="29" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>45319</v>
       </c>
       <c r="B29" s="2">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>111</v>
       </c>
       <c r="C29" s="2">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>112</v>
       </c>
       <c r="D29" s="2">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>110</v>
       </c>
       <c r="E29" s="2">
@@ -10757,7 +14099,7 @@
         <v>3</v>
       </c>
       <c r="I29" s="2">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>3.3571428571428572</v>
       </c>
       <c r="J29" s="2">
@@ -10769,51 +14111,51 @@
         <v>2</v>
       </c>
       <c r="M29" s="2">
-        <f>D28-D29</f>
+        <f t="shared" si="21"/>
         <v>-2</v>
       </c>
       <c r="N29" t="b">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>1</v>
       </c>
       <c r="O29" t="b">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>1</v>
       </c>
       <c r="P29" t="b">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>1</v>
       </c>
       <c r="Q29" s="2">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>2</v>
       </c>
       <c r="R29" s="2">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>1.1428571428571428</v>
       </c>
       <c r="S29" s="2">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>16</v>
       </c>
       <c r="U29" t="b">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="V29" t="b">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="W29" t="b">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="X29" s="2">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="Y29">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>1.2142857142857142</v>
       </c>
       <c r="Z29" s="2">
@@ -10821,23 +14163,23 @@
         <v>17</v>
       </c>
       <c r="AB29" s="10">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>34.042553191489361</v>
       </c>
       <c r="AC29" s="10">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>36.170212765957444</v>
       </c>
       <c r="AD29" s="2">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>-2.1276595744680833</v>
       </c>
       <c r="AE29" s="2">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>70.212765957446805</v>
       </c>
       <c r="AF29" s="10">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>3.0303030303030281</v>
       </c>
       <c r="AG29" s="2">
@@ -10847,19 +14189,19 @@
     </row>
     <row r="30" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>45320</v>
       </c>
       <c r="B30" s="2">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>112</v>
       </c>
       <c r="C30" s="2">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>113</v>
       </c>
       <c r="D30" s="2">
-        <f t="shared" si="37"/>
+        <f t="shared" si="38"/>
         <v>111</v>
       </c>
       <c r="E30" s="2">
@@ -10879,7 +14221,7 @@
         <v>2</v>
       </c>
       <c r="I30" s="2">
-        <f t="shared" si="38"/>
+        <f t="shared" si="39"/>
         <v>3.3571428571428572</v>
       </c>
       <c r="J30" s="2">
@@ -10891,51 +14233,51 @@
         <v>1</v>
       </c>
       <c r="M30" s="2">
-        <f>D29-D30</f>
+        <f t="shared" si="21"/>
         <v>-1</v>
       </c>
       <c r="N30" t="b">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>1</v>
       </c>
       <c r="O30" t="b">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>1</v>
       </c>
       <c r="P30" t="b">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>1</v>
       </c>
       <c r="Q30" s="2">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>1</v>
       </c>
       <c r="R30" s="2">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>1.1428571428571428</v>
       </c>
       <c r="S30" s="2">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>16</v>
       </c>
       <c r="U30" t="b">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="V30" t="b">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="W30" t="b">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="X30" s="2">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="Y30">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>1.2142857142857142</v>
       </c>
       <c r="Z30" s="2">
@@ -10943,23 +14285,23 @@
         <v>17</v>
       </c>
       <c r="AB30" s="10">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>34.042553191489361</v>
       </c>
       <c r="AC30" s="10">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>36.170212765957444</v>
       </c>
       <c r="AD30" s="2">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>-2.1276595744680833</v>
       </c>
       <c r="AE30" s="2">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>70.212765957446805</v>
       </c>
       <c r="AF30" s="10">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>3.0303030303030281</v>
       </c>
       <c r="AG30" s="2">
@@ -10969,7 +14311,7 @@
     </row>
     <row r="31" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v>45321</v>
       </c>
       <c r="B31" s="2">
@@ -11013,51 +14355,51 @@
         <v>1</v>
       </c>
       <c r="M31" s="2">
-        <f>D30-D31</f>
+        <f t="shared" si="21"/>
         <v>-1</v>
       </c>
       <c r="N31" t="b">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v>1</v>
       </c>
       <c r="O31" t="b">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v>1</v>
       </c>
       <c r="P31" t="b">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v>1</v>
       </c>
       <c r="Q31" s="2">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v>1</v>
       </c>
       <c r="R31" s="2">
-        <f t="shared" si="39"/>
+        <f t="shared" si="40"/>
         <v>1.2142857142857142</v>
       </c>
       <c r="S31" s="2">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v>17</v>
       </c>
       <c r="U31" t="b">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="V31" t="b">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="W31" t="b">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="X31" s="2">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="Y31">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v>0.2857142857142857</v>
       </c>
       <c r="Z31" s="2">
@@ -11065,23 +14407,23 @@
         <v>4</v>
       </c>
       <c r="AB31" s="10">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v>48.571428571428562</v>
       </c>
       <c r="AC31" s="10">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v>11.428571428571429</v>
       </c>
       <c r="AD31" s="2">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v>37.142857142857132</v>
       </c>
       <c r="AE31" s="2">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v>59.999999999999993</v>
       </c>
       <c r="AF31" s="10">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v>61.904761904761898</v>
       </c>
       <c r="AG31" s="2">
@@ -11669,7 +15011,7 @@
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="G19" s="13"/>
+      <c r="G19" s="2"/>
       <c r="J19" t="s">
         <v>45</v>
       </c>
@@ -11810,7 +15152,7 @@
         <v>99</v>
       </c>
       <c r="G6" s="10">
-        <f>((B6-F6)/(E6-F6))*100</f>
+        <f t="shared" ref="G6:G16" si="0">((B6-F6)/(E6-F6))*100</f>
         <v>60</v>
       </c>
     </row>
@@ -11832,15 +15174,15 @@
         <v>103</v>
       </c>
       <c r="E7" s="2">
-        <f t="shared" ref="E7:E16" si="0">MAX(C3:C7)</f>
+        <f t="shared" ref="E7:E16" si="1">MAX(C3:C7)</f>
         <v>105</v>
       </c>
       <c r="F7" s="2">
-        <f t="shared" ref="F7:F16" si="1">MIN(D3:D7)</f>
+        <f t="shared" ref="F7:F16" si="2">MIN(D3:D7)</f>
         <v>100</v>
       </c>
       <c r="G7" s="10">
-        <f>((B7-F7)/(E7-F7))*100</f>
+        <f t="shared" si="0"/>
         <v>80</v>
       </c>
     </row>
@@ -11862,15 +15204,15 @@
         <v>105</v>
       </c>
       <c r="E8" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>107</v>
       </c>
       <c r="F8" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>100</v>
       </c>
       <c r="G8" s="10">
-        <f>((B8-F8)/(E8-F8))*100</f>
+        <f t="shared" si="0"/>
         <v>85.714285714285708</v>
       </c>
       <c r="H8" s="10">
@@ -11896,19 +15238,19 @@
         <v>104</v>
       </c>
       <c r="E9" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>107</v>
       </c>
       <c r="F9" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>101</v>
       </c>
       <c r="G9" s="10">
-        <f>((B9-F9)/(E9-F9))*100</f>
+        <f t="shared" si="0"/>
         <v>66.666666666666657</v>
       </c>
       <c r="H9" s="10">
-        <f t="shared" ref="H9:H16" si="2">AVERAGE(G7:G9)</f>
+        <f t="shared" ref="H9:H16" si="3">AVERAGE(G7:G9)</f>
         <v>77.460317460317455</v>
       </c>
     </row>
@@ -11930,19 +15272,19 @@
         <v>106</v>
       </c>
       <c r="E10" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>108</v>
       </c>
       <c r="F10" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>101</v>
       </c>
       <c r="G10" s="10">
-        <f>((B10-F10)/(E10-F10))*100</f>
+        <f t="shared" si="0"/>
         <v>85.714285714285708</v>
       </c>
       <c r="H10" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>79.365079365079353</v>
       </c>
     </row>
@@ -11964,19 +15306,19 @@
         <v>107</v>
       </c>
       <c r="E11" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>109</v>
       </c>
       <c r="F11" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>103</v>
       </c>
       <c r="G11" s="10">
-        <f>((B11-F11)/(E11-F11))*100</f>
+        <f t="shared" si="0"/>
         <v>83.333333333333343</v>
       </c>
       <c r="H11" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>78.571428571428569</v>
       </c>
     </row>
@@ -11998,19 +15340,19 @@
         <v>109</v>
       </c>
       <c r="E12" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>111</v>
       </c>
       <c r="F12" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>104</v>
       </c>
       <c r="G12" s="10">
-        <f>((B12-F12)/(E12-F12))*100</f>
+        <f t="shared" si="0"/>
         <v>85.714285714285708</v>
       </c>
       <c r="H12" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>84.920634920634924</v>
       </c>
     </row>
@@ -12032,19 +15374,19 @@
         <v>108</v>
       </c>
       <c r="E13" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>111</v>
       </c>
       <c r="F13" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>104</v>
       </c>
       <c r="G13" s="10">
-        <f>((B13-F13)/(E13-F13))*100</f>
+        <f t="shared" si="0"/>
         <v>71.428571428571431</v>
       </c>
       <c r="H13" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>80.158730158730165</v>
       </c>
     </row>
@@ -12066,19 +15408,19 @@
         <v>110</v>
       </c>
       <c r="E14" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>112</v>
       </c>
       <c r="F14" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>106</v>
       </c>
       <c r="G14" s="10">
-        <f>((B14-F14)/(E14-F14))*100</f>
+        <f t="shared" si="0"/>
         <v>83.333333333333343</v>
       </c>
       <c r="H14" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>80.158730158730165</v>
       </c>
     </row>
@@ -12100,19 +15442,19 @@
         <v>111</v>
       </c>
       <c r="E15" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>113</v>
       </c>
       <c r="F15" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>107</v>
       </c>
       <c r="G15" s="10">
-        <f>((B15-F15)/(E15-F15))*100</f>
+        <f t="shared" si="0"/>
         <v>83.333333333333343</v>
       </c>
       <c r="H15" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>79.365079365079367</v>
       </c>
     </row>
@@ -12134,19 +15476,19 @@
         <v>112</v>
       </c>
       <c r="E16" s="2">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>114</v>
       </c>
       <c r="F16" s="2">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>108</v>
       </c>
       <c r="G16" s="10">
-        <f>((B16-F16)/(E16-F16))*100</f>
+        <f t="shared" si="0"/>
         <v>83.333333333333343</v>
       </c>
       <c r="H16" s="10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>83.333333333333343</v>
       </c>
     </row>
